--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ICSME2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3700079F-56B4-43B6-B2BB-72383200165D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73EE235-941F-497C-9D46-6FDD8B80364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="225">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -856,6 +856,34 @@
   </si>
   <si>
     <t>Rightward Shift</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>code-changed_ui_element3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>specific_change(code-changed3)_1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>specific_change(code-changed3)_2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>absence</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Width Expansion</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(reload)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(relaod)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1007,12 +1035,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:T172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:T172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:W172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:W172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T171">
     <sortCondition ref="A1:A171"/>
   </sortState>
-  <tableColumns count="20">
+  <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{68F464FB-6EAB-4357-81E0-F3A065D812E5}" name="test_name" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{2881E9F4-1C48-436F-A2BA-7A4B3A2E2428}" name="effort"/>
     <tableColumn id="3" xr3:uid="{DB08D917-E1F8-4FDA-B62D-49DD2304FA6D}" name="sequence_number"/>
@@ -1037,6 +1065,9 @@
     <tableColumn id="27" xr3:uid="{CDCB13B9-5878-4EFA-971E-8FE16E08B808}" name="code-changed_ui_element2"/>
     <tableColumn id="30" xr3:uid="{C5FBAF92-D65B-4288-A376-71DCF5809C1F}" name="specific_change(code-changed2)_1"/>
     <tableColumn id="28" xr3:uid="{44118D36-35CD-4DD6-A688-3788855AFD0C}" name="specific_change(code-changed2)_2"/>
+    <tableColumn id="9" xr3:uid="{960C560C-12FE-4376-9F99-EFAFC7CCC9CA}" name="code-changed_ui_element3"/>
+    <tableColumn id="11" xr3:uid="{A890BDC9-BF79-43A8-AA1F-6E7EA04E2953}" name="specific_change(code-changed3)_1"/>
+    <tableColumn id="13" xr3:uid="{580284E3-5DD3-4067-BE91-2EA03407652F}" name="specific_change(code-changed3)_2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1359,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC39754-040A-4551-8F70-BC62970F44A3}">
-  <dimension ref="A1:T172"/>
+  <dimension ref="A1:W172"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="120.5" customWidth="1"/>
@@ -1383,11 +1414,11 @@
     <col min="19" max="19" width="34.4140625" customWidth="1"/>
     <col min="20" max="20" width="42.58203125" customWidth="1"/>
     <col min="21" max="21" width="27.9140625" customWidth="1"/>
-    <col min="22" max="22" width="161.58203125" customWidth="1"/>
-    <col min="23" max="23" width="68.58203125" customWidth="1"/>
+    <col min="22" max="22" width="33.4140625" customWidth="1"/>
+    <col min="23" max="23" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>133</v>
       </c>
@@ -1448,8 +1479,17 @@
       <c r="T1" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="U1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1498,7 +1538,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1550,7 +1590,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1602,7 +1642,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1660,7 +1700,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1715,7 +1755,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1764,7 +1804,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -1801,7 +1841,7 @@
         <v>171</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="s">
         <v>216</v>
@@ -1819,7 +1859,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1868,10 +1908,10 @@
         <v>201</v>
       </c>
       <c r="Q9" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1911,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1951,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1991,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -2031,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2071,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -2111,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -7522,7 +7562,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -7583,7 +7623,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>107</v>
       </c>
@@ -7632,7 +7672,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>100</v>
       </c>
@@ -7681,7 +7721,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -7718,7 +7758,7 @@
         <v>170</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="s">
         <v>190</v>
@@ -7732,17 +7772,23 @@
       <c r="P132" t="s">
         <v>202</v>
       </c>
-      <c r="Q132" t="s">
-        <v>214</v>
-      </c>
       <c r="R132" t="s">
         <v>209</v>
       </c>
       <c r="S132" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="U132" t="s">
+        <v>221</v>
+      </c>
+      <c r="V132" t="s">
+        <v>202</v>
+      </c>
+      <c r="W132" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -7779,7 +7825,7 @@
         <v>170</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="s">
         <v>190</v>
@@ -7793,17 +7839,23 @@
       <c r="P133" t="s">
         <v>202</v>
       </c>
-      <c r="Q133" t="s">
-        <v>189</v>
-      </c>
       <c r="R133" t="s">
         <v>209</v>
       </c>
       <c r="S133" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="U133" t="s">
+        <v>221</v>
+      </c>
+      <c r="V133" t="s">
+        <v>202</v>
+      </c>
+      <c r="W133" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>38</v>
       </c>
@@ -7840,7 +7892,7 @@
         <v>168</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="s">
         <v>217</v>
@@ -7853,7 +7905,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>38</v>
       </c>
@@ -7890,10 +7942,13 @@
         <v>168</v>
       </c>
       <c r="L135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>67</v>
       </c>
@@ -7930,10 +7985,13 @@
         <v>168</v>
       </c>
       <c r="L136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>67</v>
       </c>
@@ -7970,7 +8028,7 @@
         <v>168</v>
       </c>
       <c r="L137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="s">
         <v>217</v>
@@ -7982,7 +8040,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>118</v>
       </c>
@@ -8031,7 +8089,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>104</v>
       </c>
@@ -8068,7 +8126,7 @@
         <v>168</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" t="s">
         <v>217</v>
@@ -8080,8 +8138,11 @@
       <c r="P139" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="R139" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>39</v>
       </c>
@@ -8118,7 +8179,7 @@
         <v>168</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" t="s">
         <v>217</v>
@@ -8129,8 +8190,11 @@
       <c r="P140" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="R140" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -8179,7 +8243,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>105</v>
       </c>
@@ -8228,7 +8292,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>98</v>
       </c>
@@ -8283,7 +8347,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>98</v>
       </c>

--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ICSME2026\Data\Timeoff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73EE235-941F-497C-9D46-6FDD8B80364B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A0884F-CBE9-4830-A287-A8CE0EB4C792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="result" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">result!$A$1:$U$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">result!$A$1:$V$169</definedName>
     <definedName name="UI変更_分類">#REF!</definedName>
     <definedName name="原因_コードの差分">#REF!</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="227">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -884,6 +884,13 @@
   </si>
   <si>
     <t>(relaod)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>specific_change(target)_3</t>
+  </si>
+  <si>
+    <t>Other</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1035,12 +1042,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:W172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:W172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T171">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:X172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:X172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U171">
     <sortCondition ref="A1:A171"/>
   </sortState>
-  <tableColumns count="23">
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{68F464FB-6EAB-4357-81E0-F3A065D812E5}" name="test_name" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{2881E9F4-1C48-436F-A2BA-7A4B3A2E2428}" name="effort"/>
     <tableColumn id="3" xr3:uid="{DB08D917-E1F8-4FDA-B62D-49DD2304FA6D}" name="sequence_number"/>
@@ -1059,6 +1066,7 @@
     <tableColumn id="23" xr3:uid="{D897EA98-F2F0-4333-AEDC-DE1CDD4C5CAE}" name="is_in_scope"/>
     <tableColumn id="10" xr3:uid="{2B223E75-CC99-48FD-A118-9463B4FFF357}" name="specific_change(target)_1"/>
     <tableColumn id="12" xr3:uid="{67F024C7-92EF-47D5-9F3D-A32B8B8988D1}" name="specific_change(target)_2"/>
+    <tableColumn id="15" xr3:uid="{FC4E5D2D-85DD-4C32-BC64-2BE5BE6CDBE2}" name="specific_change(target)_3"/>
     <tableColumn id="24" xr3:uid="{85865D50-356A-495C-9092-A376B7E7C7BC}" name="code-changed_ui_element1"/>
     <tableColumn id="16" xr3:uid="{AB8E88C1-F48A-4142-A795-142CB7EA4AE8}" name="specific_change(code-changed1)_1"/>
     <tableColumn id="18" xr3:uid="{DE274286-7AE0-42F6-9647-C2DAFDF9C795}" name="specific_change(code-changed1)_2"/>
@@ -1390,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC39754-040A-4551-8F70-BC62970F44A3}">
-  <dimension ref="A1:W172"/>
+  <dimension ref="A1:X172"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="120.5" customWidth="1"/>
@@ -1406,19 +1414,19 @@
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="31.58203125" customWidth="1"/>
-    <col min="14" max="14" width="17.9140625" customWidth="1"/>
-    <col min="15" max="15" width="42.1640625" customWidth="1"/>
-    <col min="16" max="16" width="22.58203125" customWidth="1"/>
-    <col min="17" max="17" width="27.4140625" customWidth="1"/>
-    <col min="18" max="18" width="33.33203125" customWidth="1"/>
-    <col min="19" max="19" width="34.4140625" customWidth="1"/>
-    <col min="20" max="20" width="42.58203125" customWidth="1"/>
-    <col min="21" max="21" width="27.9140625" customWidth="1"/>
-    <col min="22" max="22" width="33.4140625" customWidth="1"/>
-    <col min="23" max="23" width="34.6640625" customWidth="1"/>
+    <col min="14" max="15" width="17.9140625" customWidth="1"/>
+    <col min="16" max="16" width="42.1640625" customWidth="1"/>
+    <col min="17" max="17" width="22.58203125" customWidth="1"/>
+    <col min="18" max="18" width="27.4140625" customWidth="1"/>
+    <col min="19" max="19" width="33.33203125" customWidth="1"/>
+    <col min="20" max="20" width="34.4140625" customWidth="1"/>
+    <col min="21" max="21" width="42.58203125" customWidth="1"/>
+    <col min="22" max="22" width="27.9140625" customWidth="1"/>
+    <col min="23" max="23" width="33.4140625" customWidth="1"/>
+    <col min="24" max="24" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>133</v>
       </c>
@@ -1462,34 +1470,37 @@
         <v>148</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1531,14 +1542,14 @@
       <c r="M2" t="s">
         <v>191</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>193</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1580,17 +1591,17 @@
       <c r="M3" t="s">
         <v>190</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>124</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>201</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1632,17 +1643,17 @@
       <c r="M4" t="s">
         <v>216</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>125</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>202</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1684,23 +1695,23 @@
       <c r="M5" t="s">
         <v>216</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>125</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>202</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>213</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>206</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1742,20 +1753,20 @@
       <c r="M6" t="s">
         <v>216</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>125</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>202</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>206</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1797,14 +1808,14 @@
       <c r="M7" t="s">
         <v>217</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>199</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -1846,20 +1857,20 @@
       <c r="M8" t="s">
         <v>216</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>193</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>214</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>207</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1901,17 +1912,17 @@
       <c r="M9" t="s">
         <v>217</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>126</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>201</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1951,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1991,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2031,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -2071,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2111,7 +2122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -2151,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2191,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2233,20 +2244,20 @@
       <c r="M17" t="s">
         <v>216</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>198</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>214</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>208</v>
       </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -2288,17 +2299,17 @@
       <c r="M18" t="s">
         <v>216</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>127</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>202</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -2337,11 +2348,11 @@
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -2381,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2421,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2461,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -2501,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2541,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -2581,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -2621,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2661,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2701,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2743,17 +2754,17 @@
       <c r="M29" t="s">
         <v>216</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>128</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>202</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2795,20 +2806,20 @@
       <c r="M30" t="s">
         <v>189</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>128</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>202</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>179</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -2848,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -2888,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -2928,7 +2939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -2968,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -3010,14 +3021,14 @@
       <c r="M35" t="s">
         <v>217</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>199</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -3059,14 +3070,14 @@
       <c r="M36" t="s">
         <v>217</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>199</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -3108,14 +3119,14 @@
       <c r="M37" t="s">
         <v>217</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>199</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -3157,14 +3168,14 @@
       <c r="M38" t="s">
         <v>217</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>199</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>117</v>
       </c>
@@ -3206,14 +3217,14 @@
       <c r="M39" t="s">
         <v>216</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>193</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -3253,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>57</v>
       </c>
@@ -3293,7 +3304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -3338,17 +3349,17 @@
       <c r="N42" t="s">
         <v>215</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>129</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>191</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -3393,17 +3404,17 @@
       <c r="N43" t="s">
         <v>215</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>129</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>191</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -3448,17 +3459,17 @@
       <c r="N44" t="s">
         <v>215</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>129</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>191</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -3498,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -3540,14 +3551,14 @@
       <c r="M46" t="s">
         <v>216</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>195</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -3589,14 +3600,14 @@
       <c r="M47" t="s">
         <v>216</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>197</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -3638,14 +3649,14 @@
       <c r="M48" t="s">
         <v>216</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>196</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -3690,17 +3701,17 @@
       <c r="N49" t="s">
         <v>215</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>129</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>191</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -3740,7 +3751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -3782,14 +3793,14 @@
       <c r="M51" t="s">
         <v>216</v>
       </c>
-      <c r="O51" t="s">
+      <c r="P51" t="s">
         <v>195</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -3831,14 +3842,14 @@
       <c r="M52" t="s">
         <v>216</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>195</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>103</v>
       </c>
@@ -3880,20 +3891,20 @@
       <c r="M53" t="s">
         <v>216</v>
       </c>
-      <c r="O53" t="s">
+      <c r="P53" t="s">
         <v>198</v>
       </c>
-      <c r="P53" t="s">
+      <c r="Q53" t="s">
         <v>214</v>
       </c>
-      <c r="R53" t="s">
+      <c r="S53" t="s">
         <v>208</v>
       </c>
-      <c r="S53" t="s">
+      <c r="T53" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -3935,17 +3946,17 @@
       <c r="M54" t="s">
         <v>216</v>
       </c>
-      <c r="O54" t="s">
+      <c r="P54" t="s">
         <v>127</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>202</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -3987,20 +3998,20 @@
       <c r="M55" t="s">
         <v>216</v>
       </c>
-      <c r="O55" t="s">
+      <c r="P55" t="s">
         <v>198</v>
       </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
         <v>214</v>
       </c>
-      <c r="R55" t="s">
+      <c r="S55" t="s">
         <v>208</v>
       </c>
-      <c r="S55" t="s">
+      <c r="T55" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -4042,17 +4053,17 @@
       <c r="M56" t="s">
         <v>216</v>
       </c>
-      <c r="O56" t="s">
+      <c r="P56" t="s">
         <v>127</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>202</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -4097,14 +4108,14 @@
       <c r="N57" t="s">
         <v>215</v>
       </c>
-      <c r="O57" t="s">
+      <c r="P57" t="s">
         <v>194</v>
       </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -4146,14 +4157,14 @@
       <c r="M58" t="s">
         <v>216</v>
       </c>
-      <c r="O58" t="s">
+      <c r="P58" t="s">
         <v>197</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -4195,14 +4206,14 @@
       <c r="M59" t="s">
         <v>216</v>
       </c>
-      <c r="O59" t="s">
+      <c r="P59" t="s">
         <v>196</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -4247,14 +4258,14 @@
       <c r="N60" t="s">
         <v>215</v>
       </c>
-      <c r="O60" t="s">
+      <c r="P60" t="s">
         <v>194</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -4296,20 +4307,20 @@
       <c r="M61" t="s">
         <v>216</v>
       </c>
-      <c r="O61" t="s">
+      <c r="P61" t="s">
         <v>198</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>214</v>
       </c>
-      <c r="R61" t="s">
+      <c r="S61" t="s">
         <v>208</v>
       </c>
-      <c r="S61" t="s">
+      <c r="T61" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>102</v>
       </c>
@@ -4351,17 +4362,17 @@
       <c r="M62" t="s">
         <v>216</v>
       </c>
-      <c r="O62" t="s">
+      <c r="P62" t="s">
         <v>127</v>
       </c>
-      <c r="P62" t="s">
+      <c r="Q62" t="s">
         <v>202</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -4403,20 +4414,20 @@
       <c r="M63" t="s">
         <v>216</v>
       </c>
-      <c r="O63" t="s">
+      <c r="P63" t="s">
         <v>198</v>
       </c>
-      <c r="P63" t="s">
+      <c r="Q63" t="s">
         <v>214</v>
       </c>
-      <c r="R63" t="s">
+      <c r="S63" t="s">
         <v>208</v>
       </c>
-      <c r="S63" t="s">
+      <c r="T63" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -4458,14 +4469,14 @@
       <c r="M64" t="s">
         <v>216</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P64" t="s">
         <v>127</v>
       </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -4510,14 +4521,14 @@
       <c r="N65" t="s">
         <v>215</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P65" t="s">
         <v>194</v>
       </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -4557,7 +4568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4597,7 +4608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4639,14 +4650,14 @@
       <c r="M68" t="s">
         <v>216</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>197</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -4686,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -4726,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -4768,14 +4779,14 @@
       <c r="M71" t="s">
         <v>216</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P71" t="s">
         <v>196</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -4820,14 +4831,14 @@
       <c r="N72" t="s">
         <v>215</v>
       </c>
-      <c r="O72" t="s">
+      <c r="P72" t="s">
         <v>194</v>
       </c>
-      <c r="P72" t="s">
+      <c r="Q72" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -4869,14 +4880,14 @@
       <c r="M73" t="s">
         <v>216</v>
       </c>
-      <c r="O73" t="s">
+      <c r="P73" t="s">
         <v>195</v>
       </c>
-      <c r="P73" t="s">
+      <c r="Q73" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -4918,14 +4929,14 @@
       <c r="M74" t="s">
         <v>216</v>
       </c>
-      <c r="O74" t="s">
+      <c r="P74" t="s">
         <v>195</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -4967,14 +4978,14 @@
       <c r="M75" t="s">
         <v>216</v>
       </c>
-      <c r="O75" t="s">
+      <c r="P75" t="s">
         <v>195</v>
       </c>
-      <c r="P75" t="s">
+      <c r="Q75" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -5014,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -5059,17 +5070,17 @@
       <c r="N77" t="s">
         <v>215</v>
       </c>
-      <c r="O77" t="s">
+      <c r="P77" t="s">
         <v>129</v>
       </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
         <v>191</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="R77" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -5111,14 +5122,14 @@
       <c r="M78" t="s">
         <v>216</v>
       </c>
-      <c r="O78" t="s">
+      <c r="P78" t="s">
         <v>195</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q78" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -5160,14 +5171,14 @@
       <c r="M79" t="s">
         <v>216</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P79" t="s">
         <v>197</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -5209,14 +5220,14 @@
       <c r="M80" t="s">
         <v>216</v>
       </c>
-      <c r="O80" t="s">
+      <c r="P80" t="s">
         <v>196</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -5261,17 +5272,17 @@
       <c r="N81" t="s">
         <v>215</v>
       </c>
-      <c r="O81" t="s">
+      <c r="P81" t="s">
         <v>129</v>
       </c>
-      <c r="P81" t="s">
+      <c r="Q81" t="s">
         <v>191</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="R81" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5311,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -5351,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -5393,14 +5404,14 @@
       <c r="M84" t="s">
         <v>216</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P84" t="s">
         <v>195</v>
       </c>
-      <c r="P84" t="s">
+      <c r="Q84" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -5445,17 +5456,17 @@
       <c r="N85" t="s">
         <v>215</v>
       </c>
-      <c r="O85" t="s">
+      <c r="P85" t="s">
         <v>129</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q85" t="s">
         <v>191</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="R85" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -5497,14 +5508,14 @@
       <c r="M86" t="s">
         <v>216</v>
       </c>
-      <c r="O86" t="s">
+      <c r="P86" t="s">
         <v>195</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q86" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -5546,14 +5557,14 @@
       <c r="M87" t="s">
         <v>216</v>
       </c>
-      <c r="O87" t="s">
+      <c r="P87" t="s">
         <v>197</v>
       </c>
-      <c r="P87" t="s">
+      <c r="Q87" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -5595,14 +5606,14 @@
       <c r="M88" t="s">
         <v>216</v>
       </c>
-      <c r="O88" t="s">
+      <c r="P88" t="s">
         <v>196</v>
       </c>
-      <c r="P88" t="s">
+      <c r="Q88" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -5644,14 +5655,14 @@
       <c r="M89" t="s">
         <v>216</v>
       </c>
-      <c r="O89" t="s">
+      <c r="P89" t="s">
         <v>195</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q89" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -5696,17 +5707,17 @@
       <c r="N90" t="s">
         <v>215</v>
       </c>
-      <c r="O90" t="s">
+      <c r="P90" t="s">
         <v>129</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q90" t="s">
         <v>191</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="R90" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -5751,17 +5762,17 @@
       <c r="N91" t="s">
         <v>215</v>
       </c>
-      <c r="O91" t="s">
+      <c r="P91" t="s">
         <v>129</v>
       </c>
-      <c r="P91" t="s">
+      <c r="Q91" t="s">
         <v>191</v>
       </c>
-      <c r="Q91" t="s">
+      <c r="R91" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -5806,17 +5817,17 @@
       <c r="N92" t="s">
         <v>215</v>
       </c>
-      <c r="O92" t="s">
+      <c r="P92" t="s">
         <v>129</v>
       </c>
-      <c r="P92" t="s">
+      <c r="Q92" t="s">
         <v>191</v>
       </c>
-      <c r="Q92" t="s">
+      <c r="R92" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -5856,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -5896,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -5938,14 +5949,14 @@
       <c r="M95" t="s">
         <v>216</v>
       </c>
-      <c r="O95" t="s">
+      <c r="P95" t="s">
         <v>197</v>
       </c>
-      <c r="P95" t="s">
+      <c r="Q95" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -5987,14 +5998,14 @@
       <c r="M96" t="s">
         <v>216</v>
       </c>
-      <c r="O96" t="s">
+      <c r="P96" t="s">
         <v>196</v>
       </c>
-      <c r="P96" t="s">
+      <c r="Q96" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>80</v>
       </c>
@@ -6039,17 +6050,17 @@
       <c r="N97" t="s">
         <v>215</v>
       </c>
-      <c r="O97" t="s">
+      <c r="P97" t="s">
         <v>129</v>
       </c>
-      <c r="P97" t="s">
+      <c r="Q97" t="s">
         <v>191</v>
       </c>
-      <c r="Q97" t="s">
+      <c r="R97" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -6089,7 +6100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -6131,14 +6142,14 @@
       <c r="M99" t="s">
         <v>216</v>
       </c>
-      <c r="O99" t="s">
+      <c r="P99" t="s">
         <v>195</v>
       </c>
-      <c r="P99" t="s">
+      <c r="Q99" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>80</v>
       </c>
@@ -6180,14 +6191,14 @@
       <c r="M100" t="s">
         <v>216</v>
       </c>
-      <c r="O100" t="s">
+      <c r="P100" t="s">
         <v>195</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q100" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -6229,14 +6240,14 @@
       <c r="M101" t="s">
         <v>216</v>
       </c>
-      <c r="O101" t="s">
+      <c r="P101" t="s">
         <v>195</v>
       </c>
-      <c r="P101" t="s">
+      <c r="Q101" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -6281,17 +6292,17 @@
       <c r="N102" t="s">
         <v>215</v>
       </c>
-      <c r="O102" t="s">
+      <c r="P102" t="s">
         <v>129</v>
       </c>
-      <c r="P102" t="s">
+      <c r="Q102" t="s">
         <v>191</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="R102" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -6333,14 +6344,14 @@
       <c r="M103" t="s">
         <v>216</v>
       </c>
-      <c r="O103" t="s">
+      <c r="P103" t="s">
         <v>195</v>
       </c>
-      <c r="P103" t="s">
+      <c r="Q103" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -6382,14 +6393,14 @@
       <c r="M104" t="s">
         <v>216</v>
       </c>
-      <c r="O104" t="s">
+      <c r="P104" t="s">
         <v>197</v>
       </c>
-      <c r="P104" t="s">
+      <c r="Q104" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -6431,14 +6442,14 @@
       <c r="M105" t="s">
         <v>216</v>
       </c>
-      <c r="O105" t="s">
+      <c r="P105" t="s">
         <v>196</v>
       </c>
-      <c r="P105" t="s">
+      <c r="Q105" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -6478,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -6523,17 +6534,17 @@
       <c r="N107" t="s">
         <v>215</v>
       </c>
-      <c r="O107" t="s">
+      <c r="P107" t="s">
         <v>129</v>
       </c>
-      <c r="P107" t="s">
+      <c r="Q107" t="s">
         <v>191</v>
       </c>
-      <c r="Q107" t="s">
+      <c r="R107" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -6578,17 +6589,17 @@
       <c r="N108" t="s">
         <v>215</v>
       </c>
-      <c r="O108" t="s">
+      <c r="P108" t="s">
         <v>129</v>
       </c>
-      <c r="P108" t="s">
+      <c r="Q108" t="s">
         <v>191</v>
       </c>
-      <c r="Q108" t="s">
+      <c r="R108" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -6630,14 +6641,14 @@
       <c r="M109" t="s">
         <v>216</v>
       </c>
-      <c r="O109" t="s">
+      <c r="P109" t="s">
         <v>197</v>
       </c>
-      <c r="P109" t="s">
+      <c r="Q109" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -6679,14 +6690,14 @@
       <c r="M110" t="s">
         <v>216</v>
       </c>
-      <c r="O110" t="s">
+      <c r="P110" t="s">
         <v>196</v>
       </c>
-      <c r="P110" t="s">
+      <c r="Q110" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -6731,17 +6742,17 @@
       <c r="N111" t="s">
         <v>215</v>
       </c>
-      <c r="O111" t="s">
+      <c r="P111" t="s">
         <v>129</v>
       </c>
-      <c r="P111" t="s">
+      <c r="Q111" t="s">
         <v>191</v>
       </c>
-      <c r="Q111" t="s">
+      <c r="R111" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -6786,17 +6797,17 @@
       <c r="N112" t="s">
         <v>215</v>
       </c>
-      <c r="O112" t="s">
+      <c r="P112" t="s">
         <v>129</v>
       </c>
-      <c r="P112" t="s">
+      <c r="Q112" t="s">
         <v>191</v>
       </c>
-      <c r="Q112" t="s">
+      <c r="R112" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>64</v>
       </c>
@@ -6836,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -6878,14 +6889,14 @@
       <c r="M114" t="s">
         <v>216</v>
       </c>
-      <c r="O114" t="s">
+      <c r="P114" t="s">
         <v>195</v>
       </c>
-      <c r="P114" t="s">
+      <c r="Q114" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>64</v>
       </c>
@@ -6927,14 +6938,14 @@
       <c r="M115" t="s">
         <v>216</v>
       </c>
-      <c r="O115" t="s">
+      <c r="P115" t="s">
         <v>195</v>
       </c>
-      <c r="P115" t="s">
+      <c r="Q115" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -6976,14 +6987,14 @@
       <c r="M116" t="s">
         <v>216</v>
       </c>
-      <c r="O116" t="s">
+      <c r="P116" t="s">
         <v>195</v>
       </c>
-      <c r="P116" t="s">
+      <c r="Q116" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>81</v>
       </c>
@@ -7025,14 +7036,14 @@
       <c r="M117" t="s">
         <v>216</v>
       </c>
-      <c r="O117" t="s">
+      <c r="P117" t="s">
         <v>195</v>
       </c>
-      <c r="P117" t="s">
+      <c r="Q117" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>81</v>
       </c>
@@ -7074,14 +7085,14 @@
       <c r="M118" t="s">
         <v>216</v>
       </c>
-      <c r="O118" t="s">
+      <c r="P118" t="s">
         <v>195</v>
       </c>
-      <c r="P118" t="s">
+      <c r="Q118" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>111</v>
       </c>
@@ -7123,14 +7134,14 @@
       <c r="M119" t="s">
         <v>216</v>
       </c>
-      <c r="O119" t="s">
+      <c r="P119" t="s">
         <v>195</v>
       </c>
-      <c r="P119" t="s">
+      <c r="Q119" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -7170,7 +7181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -7210,7 +7221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -7250,7 +7261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -7290,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -7332,17 +7343,17 @@
       <c r="M124" t="s">
         <v>190</v>
       </c>
-      <c r="O124" t="s">
+      <c r="P124" t="s">
         <v>124</v>
       </c>
-      <c r="P124" t="s">
+      <c r="Q124" t="s">
         <v>201</v>
       </c>
-      <c r="Q124" t="s">
+      <c r="R124" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>85</v>
       </c>
@@ -7384,17 +7395,17 @@
       <c r="M125" t="s">
         <v>216</v>
       </c>
-      <c r="O125" t="s">
+      <c r="P125" t="s">
         <v>125</v>
       </c>
-      <c r="P125" t="s">
+      <c r="Q125" t="s">
         <v>202</v>
       </c>
-      <c r="Q125" t="s">
+      <c r="R125" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>35</v>
       </c>
@@ -7436,26 +7447,26 @@
       <c r="M126" t="s">
         <v>216</v>
       </c>
-      <c r="O126" t="s">
+      <c r="P126" t="s">
         <v>125</v>
       </c>
-      <c r="P126" t="s">
+      <c r="Q126" t="s">
         <v>202</v>
       </c>
-      <c r="Q126" t="s">
+      <c r="R126" t="s">
         <v>213</v>
       </c>
-      <c r="R126" t="s">
+      <c r="S126" t="s">
         <v>206</v>
       </c>
-      <c r="S126" t="s">
+      <c r="T126" t="s">
         <v>205</v>
       </c>
-      <c r="T126" t="s">
+      <c r="U126" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -7497,20 +7508,20 @@
       <c r="M127" t="s">
         <v>216</v>
       </c>
-      <c r="O127" t="s">
+      <c r="P127" t="s">
         <v>125</v>
       </c>
-      <c r="P127" t="s">
+      <c r="Q127" t="s">
         <v>202</v>
       </c>
-      <c r="R127" t="s">
+      <c r="S127" t="s">
         <v>206</v>
       </c>
-      <c r="S127" t="s">
+      <c r="T127" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>113</v>
       </c>
@@ -7552,17 +7563,17 @@
       <c r="M128" t="s">
         <v>215</v>
       </c>
-      <c r="O128" t="s">
+      <c r="P128" t="s">
         <v>124</v>
       </c>
-      <c r="P128" t="s">
+      <c r="Q128" t="s">
         <v>201</v>
       </c>
-      <c r="Q128" t="s">
+      <c r="R128" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -7604,26 +7615,26 @@
       <c r="M129" t="s">
         <v>216</v>
       </c>
-      <c r="O129" t="s">
+      <c r="P129" t="s">
         <v>125</v>
       </c>
-      <c r="P129" t="s">
+      <c r="Q129" t="s">
         <v>202</v>
       </c>
-      <c r="Q129" t="s">
+      <c r="R129" t="s">
         <v>213</v>
       </c>
-      <c r="R129" t="s">
+      <c r="S129" t="s">
         <v>206</v>
       </c>
-      <c r="S129" t="s">
+      <c r="T129" t="s">
         <v>205</v>
       </c>
-      <c r="T129" t="s">
+      <c r="U129" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>107</v>
       </c>
@@ -7665,14 +7676,14 @@
       <c r="M130" t="s">
         <v>191</v>
       </c>
-      <c r="O130" t="s">
+      <c r="P130" t="s">
         <v>193</v>
       </c>
-      <c r="P130" t="s">
+      <c r="Q130" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>100</v>
       </c>
@@ -7714,14 +7725,14 @@
       <c r="M131" t="s">
         <v>191</v>
       </c>
-      <c r="O131" t="s">
+      <c r="P131" t="s">
         <v>193</v>
       </c>
-      <c r="P131" t="s">
+      <c r="Q131" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -7767,28 +7778,34 @@
         <v>217</v>
       </c>
       <c r="O132" t="s">
+        <v>222</v>
+      </c>
+      <c r="P132" t="s">
         <v>130</v>
       </c>
-      <c r="P132" t="s">
+      <c r="Q132" t="s">
         <v>202</v>
       </c>
       <c r="R132" t="s">
+        <v>222</v>
+      </c>
+      <c r="S132" t="s">
         <v>209</v>
       </c>
-      <c r="S132" t="s">
-        <v>210</v>
-      </c>
-      <c r="U132" t="s">
+      <c r="T132" t="s">
+        <v>226</v>
+      </c>
+      <c r="V132" t="s">
         <v>221</v>
       </c>
-      <c r="V132" t="s">
+      <c r="W132" t="s">
         <v>202</v>
       </c>
-      <c r="W132" t="s">
+      <c r="X132" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -7834,28 +7851,34 @@
         <v>217</v>
       </c>
       <c r="O133" t="s">
+        <v>222</v>
+      </c>
+      <c r="P133" t="s">
         <v>130</v>
       </c>
-      <c r="P133" t="s">
+      <c r="Q133" t="s">
         <v>202</v>
       </c>
       <c r="R133" t="s">
+        <v>222</v>
+      </c>
+      <c r="S133" t="s">
         <v>209</v>
       </c>
-      <c r="S133" t="s">
+      <c r="T133" t="s">
         <v>210</v>
       </c>
-      <c r="U133" t="s">
+      <c r="V133" t="s">
         <v>221</v>
       </c>
-      <c r="V133" t="s">
+      <c r="W133" t="s">
         <v>202</v>
       </c>
-      <c r="W133" t="s">
+      <c r="X133" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>38</v>
       </c>
@@ -7898,14 +7921,15 @@
         <v>217</v>
       </c>
       <c r="N134" s="4"/>
-      <c r="O134" t="s">
+      <c r="O134" s="4"/>
+      <c r="P134" t="s">
         <v>199</v>
       </c>
-      <c r="P134" t="s">
+      <c r="Q134" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>38</v>
       </c>
@@ -7944,11 +7968,11 @@
       <c r="L135">
         <v>1</v>
       </c>
-      <c r="O135" t="s">
+      <c r="P135" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>67</v>
       </c>
@@ -7987,11 +8011,11 @@
       <c r="L136">
         <v>1</v>
       </c>
-      <c r="O136" t="s">
+      <c r="P136" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>67</v>
       </c>
@@ -8033,14 +8057,14 @@
       <c r="M137" t="s">
         <v>217</v>
       </c>
-      <c r="O137" t="s">
+      <c r="P137" t="s">
         <v>199</v>
       </c>
-      <c r="P137" t="s">
+      <c r="Q137" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>118</v>
       </c>
@@ -8082,14 +8106,14 @@
       <c r="M138" t="s">
         <v>216</v>
       </c>
-      <c r="O138" t="s">
+      <c r="P138" t="s">
         <v>193</v>
       </c>
-      <c r="P138" t="s">
+      <c r="Q138" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>104</v>
       </c>
@@ -8132,17 +8156,18 @@
         <v>217</v>
       </c>
       <c r="N139" s="4"/>
-      <c r="O139" t="s">
+      <c r="O139" s="4"/>
+      <c r="P139" t="s">
         <v>199</v>
       </c>
-      <c r="P139" t="s">
+      <c r="Q139" t="s">
         <v>214</v>
       </c>
-      <c r="R139" t="s">
+      <c r="S139" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>39</v>
       </c>
@@ -8184,17 +8209,17 @@
       <c r="M140" t="s">
         <v>217</v>
       </c>
-      <c r="O140" t="s">
+      <c r="P140" t="s">
         <v>199</v>
       </c>
-      <c r="P140" t="s">
+      <c r="Q140" t="s">
         <v>214</v>
       </c>
-      <c r="R140" t="s">
+      <c r="S140" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -8236,14 +8261,14 @@
       <c r="M141" t="s">
         <v>216</v>
       </c>
-      <c r="O141" t="s">
+      <c r="P141" t="s">
         <v>193</v>
       </c>
-      <c r="P141" t="s">
+      <c r="Q141" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>105</v>
       </c>
@@ -8285,14 +8310,14 @@
       <c r="M142" t="s">
         <v>217</v>
       </c>
-      <c r="O142" t="s">
+      <c r="P142" t="s">
         <v>199</v>
       </c>
-      <c r="P142" t="s">
+      <c r="Q142" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>98</v>
       </c>
@@ -8337,17 +8362,17 @@
       <c r="N143" t="s">
         <v>215</v>
       </c>
-      <c r="O143" t="s">
+      <c r="P143" t="s">
         <v>129</v>
       </c>
-      <c r="P143" t="s">
+      <c r="Q143" t="s">
         <v>191</v>
       </c>
-      <c r="Q143" t="s">
+      <c r="R143" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>98</v>
       </c>
@@ -8389,14 +8414,14 @@
       <c r="M144" t="s">
         <v>216</v>
       </c>
-      <c r="O144" t="s">
+      <c r="P144" t="s">
         <v>195</v>
       </c>
-      <c r="P144" t="s">
+      <c r="Q144" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>98</v>
       </c>
@@ -8438,14 +8463,14 @@
       <c r="M145" t="s">
         <v>216</v>
       </c>
-      <c r="O145" t="s">
+      <c r="P145" t="s">
         <v>197</v>
       </c>
-      <c r="P145" t="s">
+      <c r="Q145" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>98</v>
       </c>
@@ -8487,14 +8512,14 @@
       <c r="M146" t="s">
         <v>216</v>
       </c>
-      <c r="O146" t="s">
+      <c r="P146" t="s">
         <v>196</v>
       </c>
-      <c r="P146" t="s">
+      <c r="Q146" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>90</v>
       </c>
@@ -8539,17 +8564,17 @@
       <c r="N147" t="s">
         <v>215</v>
       </c>
-      <c r="O147" t="s">
+      <c r="P147" t="s">
         <v>129</v>
       </c>
-      <c r="P147" t="s">
+      <c r="Q147" t="s">
         <v>191</v>
       </c>
-      <c r="Q147" t="s">
+      <c r="R147" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>90</v>
       </c>
@@ -8591,14 +8616,14 @@
       <c r="M148" t="s">
         <v>216</v>
       </c>
-      <c r="O148" t="s">
+      <c r="P148" t="s">
         <v>195</v>
       </c>
-      <c r="P148" t="s">
+      <c r="Q148" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>90</v>
       </c>
@@ -8640,14 +8665,14 @@
       <c r="M149" t="s">
         <v>216</v>
       </c>
-      <c r="O149" t="s">
+      <c r="P149" t="s">
         <v>197</v>
       </c>
-      <c r="P149" t="s">
+      <c r="Q149" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>90</v>
       </c>
@@ -8689,14 +8714,14 @@
       <c r="M150" t="s">
         <v>216</v>
       </c>
-      <c r="O150" t="s">
+      <c r="P150" t="s">
         <v>196</v>
       </c>
-      <c r="P150" t="s">
+      <c r="Q150" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -8738,17 +8763,17 @@
       <c r="M151" t="s">
         <v>217</v>
       </c>
-      <c r="O151" t="s">
+      <c r="P151" t="s">
         <v>126</v>
       </c>
-      <c r="P151" t="s">
+      <c r="Q151" t="s">
         <v>201</v>
       </c>
-      <c r="Q151" t="s">
+      <c r="R151" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -8788,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>91</v>
       </c>
@@ -8828,7 +8853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>106</v>
       </c>
@@ -8870,17 +8895,17 @@
       <c r="M154" t="s">
         <v>216</v>
       </c>
-      <c r="O154" t="s">
+      <c r="P154" t="s">
         <v>131</v>
       </c>
-      <c r="P154" t="s">
+      <c r="Q154" t="s">
         <v>202</v>
       </c>
-      <c r="Q154" t="s">
+      <c r="R154" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>122</v>
       </c>
@@ -8922,14 +8947,14 @@
       <c r="M155" t="s">
         <v>217</v>
       </c>
-      <c r="O155" t="s">
+      <c r="P155" t="s">
         <v>199</v>
       </c>
-      <c r="P155" t="s">
+      <c r="Q155" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>70</v>
       </c>
@@ -8971,14 +8996,14 @@
       <c r="M156" t="s">
         <v>216</v>
       </c>
-      <c r="O156" t="s">
+      <c r="P156" t="s">
         <v>193</v>
       </c>
-      <c r="P156" t="s">
+      <c r="Q156" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>71</v>
       </c>
@@ -9020,14 +9045,14 @@
       <c r="M157" t="s">
         <v>217</v>
       </c>
-      <c r="O157" t="s">
+      <c r="P157" t="s">
         <v>199</v>
       </c>
-      <c r="P157" t="s">
+      <c r="Q157" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>71</v>
       </c>
@@ -9069,14 +9094,14 @@
       <c r="M158" t="s">
         <v>216</v>
       </c>
-      <c r="O158" t="s">
+      <c r="P158" t="s">
         <v>193</v>
       </c>
-      <c r="P158" t="s">
+      <c r="Q158" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>112</v>
       </c>
@@ -9118,14 +9143,14 @@
       <c r="M159" t="s">
         <v>216</v>
       </c>
-      <c r="O159" t="s">
+      <c r="P159" t="s">
         <v>195</v>
       </c>
-      <c r="P159" t="s">
+      <c r="Q159" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>108</v>
       </c>
@@ -9167,14 +9192,14 @@
       <c r="M160" t="s">
         <v>191</v>
       </c>
-      <c r="O160" t="s">
+      <c r="P160" t="s">
         <v>193</v>
       </c>
-      <c r="P160" t="s">
+      <c r="Q160" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>109</v>
       </c>
@@ -9219,14 +9244,14 @@
       <c r="N161" t="s">
         <v>216</v>
       </c>
-      <c r="O161" t="s">
+      <c r="P161" t="s">
         <v>193</v>
       </c>
-      <c r="P161" t="s">
+      <c r="Q161" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>109</v>
       </c>
@@ -9271,23 +9296,23 @@
       <c r="N162" t="s">
         <v>192</v>
       </c>
-      <c r="O162" t="s">
+      <c r="P162" t="s">
         <v>193</v>
       </c>
-      <c r="P162" t="s">
+      <c r="Q162" t="s">
         <v>214</v>
       </c>
-      <c r="R162" t="s">
+      <c r="S162" t="s">
         <v>132</v>
       </c>
-      <c r="S162" t="s">
+      <c r="T162" t="s">
         <v>211</v>
       </c>
-      <c r="T162" t="s">
+      <c r="U162" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>42</v>
       </c>
@@ -9332,17 +9357,17 @@
       <c r="N163" t="s">
         <v>215</v>
       </c>
-      <c r="O163" t="s">
+      <c r="P163" t="s">
         <v>129</v>
       </c>
-      <c r="P163" t="s">
+      <c r="Q163" t="s">
         <v>191</v>
       </c>
-      <c r="Q163" t="s">
+      <c r="R163" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>42</v>
       </c>
@@ -9382,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>42</v>
       </c>
@@ -9424,14 +9449,14 @@
       <c r="M165" t="s">
         <v>216</v>
       </c>
-      <c r="O165" t="s">
+      <c r="P165" t="s">
         <v>195</v>
       </c>
-      <c r="P165" t="s">
+      <c r="Q165" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>42</v>
       </c>
@@ -9473,14 +9498,14 @@
       <c r="M166" t="s">
         <v>216</v>
       </c>
-      <c r="O166" t="s">
+      <c r="P166" t="s">
         <v>197</v>
       </c>
-      <c r="P166" t="s">
+      <c r="Q166" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>42</v>
       </c>
@@ -9522,14 +9547,14 @@
       <c r="M167" t="s">
         <v>216</v>
       </c>
-      <c r="O167" t="s">
+      <c r="P167" t="s">
         <v>196</v>
       </c>
-      <c r="P167" t="s">
+      <c r="Q167" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>42</v>
       </c>
@@ -9574,17 +9599,17 @@
       <c r="N168" t="s">
         <v>215</v>
       </c>
-      <c r="O168" t="s">
+      <c r="P168" t="s">
         <v>129</v>
       </c>
-      <c r="P168" t="s">
+      <c r="Q168" t="s">
         <v>191</v>
       </c>
-      <c r="Q168" t="s">
+      <c r="R168" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -9624,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>42</v>
       </c>
@@ -9666,14 +9691,14 @@
       <c r="M170" t="s">
         <v>216</v>
       </c>
-      <c r="O170" t="s">
+      <c r="P170" t="s">
         <v>195</v>
       </c>
-      <c r="P170" t="s">
+      <c r="Q170" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -9715,14 +9740,14 @@
       <c r="M171" t="s">
         <v>217</v>
       </c>
-      <c r="O171" t="s">
+      <c r="P171" t="s">
         <v>199</v>
       </c>
-      <c r="P171" t="s">
+      <c r="Q171" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>116</v>
       </c>
@@ -9764,10 +9789,10 @@
       <c r="M172" t="s">
         <v>216</v>
       </c>
-      <c r="O172" t="s">
+      <c r="P172" t="s">
         <v>193</v>
       </c>
-      <c r="P172" t="s">
+      <c r="Q172" t="s">
         <v>214</v>
       </c>
     </row>
@@ -9777,7 +9802,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J14 J35:J1048576" xr:uid="{3E25D0BD-7905-4B16-9F4F-719A1BAC5BA8}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U173:U1048576" xr:uid="{7CB71164-8EDD-428C-AA0E-6BDEFE0E78A5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V173:V1048576" xr:uid="{7CB71164-8EDD-428C-AA0E-6BDEFE0E78A5}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A0884F-CBE9-4830-A287-A8CE0EB4C792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131A0197-C177-4A45-9377-475106F1E0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
+    <workbookView xWindow="1440" yWindow="1440" windowWidth="14400" windowHeight="7810" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="226">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -791,10 +791,6 @@
   </si>
   <si>
     <t>Employees</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Not Found</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1470,7 +1466,7 @@
         <v>148</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>145</v>
@@ -1491,13 +1487,13 @@
         <v>151</v>
       </c>
       <c r="V1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1546,7 +1542,7 @@
         <v>193</v>
       </c>
       <c r="Q2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1595,10 +1591,10 @@
         <v>124</v>
       </c>
       <c r="Q3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1641,16 +1637,16 @@
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P4" t="s">
         <v>125</v>
       </c>
       <c r="Q4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1693,22 +1689,22 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P5" t="s">
         <v>125</v>
       </c>
       <c r="Q5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1751,19 +1747,19 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P6" t="s">
         <v>125</v>
       </c>
       <c r="Q6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1806,13 +1802,13 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P7" t="s">
         <v>199</v>
       </c>
       <c r="Q7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1855,19 +1851,19 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P8" t="s">
         <v>193</v>
       </c>
       <c r="Q8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -1910,16 +1906,16 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P9" t="s">
         <v>126</v>
       </c>
       <c r="Q9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -2242,19 +2238,19 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P17" t="s">
         <v>198</v>
       </c>
       <c r="Q17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -2297,16 +2293,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P18" t="s">
         <v>127</v>
       </c>
       <c r="Q18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -2349,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -2752,16 +2748,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P29" t="s">
         <v>128</v>
       </c>
       <c r="Q29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -2810,13 +2806,13 @@
         <v>128</v>
       </c>
       <c r="Q30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S30" t="s">
         <v>179</v>
       </c>
       <c r="T30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3019,13 +3015,13 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P35" t="s">
         <v>199</v>
       </c>
       <c r="Q35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3068,13 +3064,13 @@
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P36" t="s">
         <v>199</v>
       </c>
       <c r="Q36" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3117,13 +3113,13 @@
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P37" t="s">
         <v>199</v>
       </c>
       <c r="Q37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3166,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P38" t="s">
         <v>199</v>
       </c>
       <c r="Q38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3215,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="M39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P39" t="s">
         <v>193</v>
       </c>
       <c r="Q39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3347,7 +3343,7 @@
         <v>191</v>
       </c>
       <c r="N42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P42" t="s">
         <v>129</v>
@@ -3356,7 +3352,7 @@
         <v>191</v>
       </c>
       <c r="R42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3402,7 +3398,7 @@
         <v>191</v>
       </c>
       <c r="N43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P43" t="s">
         <v>129</v>
@@ -3411,7 +3407,7 @@
         <v>191</v>
       </c>
       <c r="R43" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3457,7 +3453,7 @@
         <v>191</v>
       </c>
       <c r="N44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P44" t="s">
         <v>129</v>
@@ -3466,7 +3462,7 @@
         <v>191</v>
       </c>
       <c r="R44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3549,13 +3545,13 @@
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P46" t="s">
         <v>195</v>
       </c>
       <c r="Q46" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3598,13 +3594,13 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P47" t="s">
         <v>197</v>
       </c>
       <c r="Q47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -3647,13 +3643,13 @@
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P48" t="s">
         <v>196</v>
       </c>
       <c r="Q48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3699,7 +3695,7 @@
         <v>191</v>
       </c>
       <c r="N49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P49" t="s">
         <v>129</v>
@@ -3708,7 +3704,7 @@
         <v>191</v>
       </c>
       <c r="R49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3791,13 +3787,13 @@
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P51" t="s">
         <v>195</v>
       </c>
       <c r="Q51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3840,13 +3836,13 @@
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P52" t="s">
         <v>195</v>
       </c>
       <c r="Q52" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3889,19 +3885,19 @@
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P53" t="s">
         <v>198</v>
       </c>
       <c r="Q53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S53" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3944,16 +3940,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P54" t="s">
         <v>127</v>
       </c>
       <c r="Q54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -3996,19 +3992,19 @@
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P55" t="s">
         <v>198</v>
       </c>
       <c r="Q55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4051,16 +4047,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P56" t="s">
         <v>127</v>
       </c>
       <c r="Q56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4103,16 +4099,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P57" t="s">
         <v>194</v>
       </c>
       <c r="Q57" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4155,13 +4151,13 @@
         <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P58" t="s">
         <v>197</v>
       </c>
       <c r="Q58" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4204,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" t="s">
         <v>196</v>
       </c>
       <c r="Q59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4253,16 +4249,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P60" t="s">
         <v>194</v>
       </c>
       <c r="Q60" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4305,19 +4301,19 @@
         <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" t="s">
         <v>198</v>
       </c>
       <c r="Q61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4360,16 +4356,16 @@
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" t="s">
         <v>127</v>
       </c>
       <c r="Q62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4412,19 +4408,19 @@
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P63" t="s">
         <v>198</v>
       </c>
       <c r="Q63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T63" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
@@ -4467,13 +4463,13 @@
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P64" t="s">
         <v>127</v>
       </c>
       <c r="Q64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4516,16 +4512,16 @@
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P65" t="s">
         <v>194</v>
       </c>
       <c r="Q65" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4648,13 +4644,13 @@
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P68" t="s">
         <v>197</v>
       </c>
       <c r="Q68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4777,13 +4773,13 @@
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P71" t="s">
         <v>196</v>
       </c>
       <c r="Q71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4826,16 +4822,16 @@
         <v>1</v>
       </c>
       <c r="M72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N72" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P72" t="s">
         <v>194</v>
       </c>
       <c r="Q72" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4878,13 +4874,13 @@
         <v>1</v>
       </c>
       <c r="M73" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P73" t="s">
         <v>195</v>
       </c>
       <c r="Q73" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4927,13 +4923,13 @@
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P74" t="s">
         <v>195</v>
       </c>
       <c r="Q74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -4976,13 +4972,13 @@
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P75" t="s">
         <v>195</v>
       </c>
       <c r="Q75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5068,7 +5064,7 @@
         <v>191</v>
       </c>
       <c r="N77" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P77" t="s">
         <v>129</v>
@@ -5077,7 +5073,7 @@
         <v>191</v>
       </c>
       <c r="R77" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5120,13 +5116,13 @@
         <v>1</v>
       </c>
       <c r="M78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P78" t="s">
         <v>195</v>
       </c>
       <c r="Q78" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5169,13 +5165,13 @@
         <v>1</v>
       </c>
       <c r="M79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P79" t="s">
         <v>197</v>
       </c>
       <c r="Q79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5218,13 +5214,13 @@
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P80" t="s">
         <v>196</v>
       </c>
       <c r="Q80" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5270,7 +5266,7 @@
         <v>191</v>
       </c>
       <c r="N81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P81" t="s">
         <v>129</v>
@@ -5279,7 +5275,7 @@
         <v>191</v>
       </c>
       <c r="R81" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5402,13 +5398,13 @@
         <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P84" t="s">
         <v>195</v>
       </c>
       <c r="Q84" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5454,7 +5450,7 @@
         <v>191</v>
       </c>
       <c r="N85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P85" t="s">
         <v>129</v>
@@ -5463,7 +5459,7 @@
         <v>191</v>
       </c>
       <c r="R85" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5506,13 +5502,13 @@
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P86" t="s">
         <v>195</v>
       </c>
       <c r="Q86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5555,13 +5551,13 @@
         <v>1</v>
       </c>
       <c r="M87" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P87" t="s">
         <v>197</v>
       </c>
       <c r="Q87" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5604,13 +5600,13 @@
         <v>1</v>
       </c>
       <c r="M88" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P88" t="s">
         <v>196</v>
       </c>
       <c r="Q88" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5653,13 +5649,13 @@
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P89" t="s">
         <v>195</v>
       </c>
       <c r="Q89" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5705,7 +5701,7 @@
         <v>191</v>
       </c>
       <c r="N90" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P90" t="s">
         <v>129</v>
@@ -5714,7 +5710,7 @@
         <v>191</v>
       </c>
       <c r="R90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5760,7 +5756,7 @@
         <v>191</v>
       </c>
       <c r="N91" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P91" t="s">
         <v>129</v>
@@ -5769,7 +5765,7 @@
         <v>191</v>
       </c>
       <c r="R91" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5815,7 +5811,7 @@
         <v>191</v>
       </c>
       <c r="N92" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P92" t="s">
         <v>129</v>
@@ -5824,7 +5820,7 @@
         <v>191</v>
       </c>
       <c r="R92" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5947,13 +5943,13 @@
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P95" t="s">
         <v>197</v>
       </c>
       <c r="Q95" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -5996,13 +5992,13 @@
         <v>1</v>
       </c>
       <c r="M96" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P96" t="s">
         <v>196</v>
       </c>
       <c r="Q96" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6048,7 +6044,7 @@
         <v>191</v>
       </c>
       <c r="N97" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P97" t="s">
         <v>129</v>
@@ -6057,7 +6053,7 @@
         <v>191</v>
       </c>
       <c r="R97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6140,13 +6136,13 @@
         <v>1</v>
       </c>
       <c r="M99" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P99" t="s">
         <v>195</v>
       </c>
       <c r="Q99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6189,13 +6185,13 @@
         <v>1</v>
       </c>
       <c r="M100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P100" t="s">
         <v>195</v>
       </c>
       <c r="Q100" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6238,13 +6234,13 @@
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P101" t="s">
         <v>195</v>
       </c>
       <c r="Q101" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6290,7 +6286,7 @@
         <v>191</v>
       </c>
       <c r="N102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P102" t="s">
         <v>129</v>
@@ -6299,7 +6295,7 @@
         <v>191</v>
       </c>
       <c r="R102" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6342,13 +6338,13 @@
         <v>1</v>
       </c>
       <c r="M103" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P103" t="s">
         <v>195</v>
       </c>
       <c r="Q103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6391,13 +6387,13 @@
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P104" t="s">
         <v>197</v>
       </c>
       <c r="Q104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6440,13 +6436,13 @@
         <v>1</v>
       </c>
       <c r="M105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P105" t="s">
         <v>196</v>
       </c>
       <c r="Q105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6532,7 +6528,7 @@
         <v>191</v>
       </c>
       <c r="N107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P107" t="s">
         <v>129</v>
@@ -6541,7 +6537,7 @@
         <v>191</v>
       </c>
       <c r="R107" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6587,7 +6583,7 @@
         <v>191</v>
       </c>
       <c r="N108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P108" t="s">
         <v>129</v>
@@ -6596,7 +6592,7 @@
         <v>191</v>
       </c>
       <c r="R108" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6639,13 +6635,13 @@
         <v>1</v>
       </c>
       <c r="M109" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P109" t="s">
         <v>197</v>
       </c>
       <c r="Q109" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6688,13 +6684,13 @@
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P110" t="s">
         <v>196</v>
       </c>
       <c r="Q110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6740,7 +6736,7 @@
         <v>191</v>
       </c>
       <c r="N111" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P111" t="s">
         <v>129</v>
@@ -6749,7 +6745,7 @@
         <v>191</v>
       </c>
       <c r="R111" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -6795,7 +6791,7 @@
         <v>191</v>
       </c>
       <c r="N112" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P112" t="s">
         <v>129</v>
@@ -6804,7 +6800,7 @@
         <v>191</v>
       </c>
       <c r="R112" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -6887,13 +6883,13 @@
         <v>1</v>
       </c>
       <c r="M114" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P114" t="s">
         <v>195</v>
       </c>
       <c r="Q114" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -6936,13 +6932,13 @@
         <v>1</v>
       </c>
       <c r="M115" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P115" t="s">
         <v>195</v>
       </c>
       <c r="Q115" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -6985,13 +6981,13 @@
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P116" t="s">
         <v>195</v>
       </c>
       <c r="Q116" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7034,13 +7030,13 @@
         <v>1</v>
       </c>
       <c r="M117" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P117" t="s">
         <v>195</v>
       </c>
       <c r="Q117" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7083,13 +7079,13 @@
         <v>1</v>
       </c>
       <c r="M118" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P118" t="s">
         <v>195</v>
       </c>
       <c r="Q118" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7132,13 +7128,13 @@
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P119" t="s">
         <v>195</v>
       </c>
       <c r="Q119" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7347,10 +7343,10 @@
         <v>124</v>
       </c>
       <c r="Q124" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7393,16 +7389,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P125" t="s">
         <v>125</v>
       </c>
       <c r="Q125" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R125" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7445,25 +7441,25 @@
         <v>1</v>
       </c>
       <c r="M126" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P126" t="s">
         <v>125</v>
       </c>
       <c r="Q126" t="s">
+        <v>201</v>
+      </c>
+      <c r="R126" t="s">
+        <v>212</v>
+      </c>
+      <c r="S126" t="s">
+        <v>205</v>
+      </c>
+      <c r="T126" t="s">
+        <v>204</v>
+      </c>
+      <c r="U126" t="s">
         <v>202</v>
-      </c>
-      <c r="R126" t="s">
-        <v>213</v>
-      </c>
-      <c r="S126" t="s">
-        <v>206</v>
-      </c>
-      <c r="T126" t="s">
-        <v>205</v>
-      </c>
-      <c r="U126" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7506,19 +7502,19 @@
         <v>1</v>
       </c>
       <c r="M127" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P127" t="s">
         <v>125</v>
       </c>
       <c r="Q127" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S127" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T127" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -7561,16 +7557,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P128" t="s">
         <v>124</v>
       </c>
       <c r="Q128" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R128" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7613,25 +7609,25 @@
         <v>1</v>
       </c>
       <c r="M129" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P129" t="s">
         <v>125</v>
       </c>
       <c r="Q129" t="s">
+        <v>201</v>
+      </c>
+      <c r="R129" t="s">
+        <v>212</v>
+      </c>
+      <c r="S129" t="s">
+        <v>205</v>
+      </c>
+      <c r="T129" t="s">
+        <v>204</v>
+      </c>
+      <c r="U129" t="s">
         <v>202</v>
-      </c>
-      <c r="R129" t="s">
-        <v>213</v>
-      </c>
-      <c r="S129" t="s">
-        <v>206</v>
-      </c>
-      <c r="T129" t="s">
-        <v>205</v>
-      </c>
-      <c r="U129" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7680,7 +7676,7 @@
         <v>193</v>
       </c>
       <c r="Q130" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7729,7 +7725,7 @@
         <v>193</v>
       </c>
       <c r="Q131" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7775,34 +7771,34 @@
         <v>190</v>
       </c>
       <c r="N132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O132" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P132" t="s">
         <v>130</v>
       </c>
       <c r="Q132" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R132" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S132" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T132" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V132" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W132" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X132" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7848,34 +7844,34 @@
         <v>190</v>
       </c>
       <c r="N133" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O133" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P133" t="s">
         <v>130</v>
       </c>
       <c r="Q133" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R133" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S133" t="s">
+        <v>208</v>
+      </c>
+      <c r="T133" t="s">
         <v>209</v>
       </c>
-      <c r="T133" t="s">
-        <v>210</v>
-      </c>
       <c r="V133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W133" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X133" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7918,7 +7914,7 @@
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
@@ -7926,7 +7922,7 @@
         <v>199</v>
       </c>
       <c r="Q134" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -7969,7 +7965,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8012,7 +8008,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8055,13 +8051,13 @@
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P137" t="s">
         <v>199</v>
       </c>
       <c r="Q137" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8104,13 +8100,13 @@
         <v>1</v>
       </c>
       <c r="M138" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P138" t="s">
         <v>193</v>
       </c>
       <c r="Q138" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8153,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="M139" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
@@ -8161,10 +8157,10 @@
         <v>199</v>
       </c>
       <c r="Q139" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S139" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8207,16 +8203,16 @@
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P140" t="s">
         <v>199</v>
       </c>
       <c r="Q140" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S140" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8259,13 +8255,13 @@
         <v>1</v>
       </c>
       <c r="M141" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P141" t="s">
         <v>193</v>
       </c>
       <c r="Q141" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8308,13 +8304,13 @@
         <v>1</v>
       </c>
       <c r="M142" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P142" t="s">
         <v>199</v>
       </c>
       <c r="Q142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8360,7 +8356,7 @@
         <v>191</v>
       </c>
       <c r="N143" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P143" t="s">
         <v>129</v>
@@ -8369,7 +8365,7 @@
         <v>191</v>
       </c>
       <c r="R143" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.55000000000000004">
@@ -8412,13 +8408,13 @@
         <v>1</v>
       </c>
       <c r="M144" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P144" t="s">
         <v>195</v>
       </c>
       <c r="Q144" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8461,13 +8457,13 @@
         <v>1</v>
       </c>
       <c r="M145" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P145" t="s">
         <v>197</v>
       </c>
       <c r="Q145" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8510,13 +8506,13 @@
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P146" t="s">
         <v>196</v>
       </c>
       <c r="Q146" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8562,7 +8558,7 @@
         <v>191</v>
       </c>
       <c r="N147" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P147" t="s">
         <v>129</v>
@@ -8571,7 +8567,7 @@
         <v>191</v>
       </c>
       <c r="R147" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8614,13 +8610,13 @@
         <v>1</v>
       </c>
       <c r="M148" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P148" t="s">
         <v>195</v>
       </c>
       <c r="Q148" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8663,13 +8659,13 @@
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P149" t="s">
         <v>197</v>
       </c>
       <c r="Q149" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8712,13 +8708,13 @@
         <v>1</v>
       </c>
       <c r="M150" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P150" t="s">
         <v>196</v>
       </c>
       <c r="Q150" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8761,16 +8757,16 @@
         <v>1</v>
       </c>
       <c r="M151" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P151" t="s">
         <v>126</v>
       </c>
       <c r="Q151" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R151" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8893,16 +8889,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P154" t="s">
         <v>131</v>
       </c>
       <c r="Q154" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R154" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8945,13 +8941,13 @@
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P155" t="s">
         <v>199</v>
       </c>
       <c r="Q155" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -8994,13 +8990,13 @@
         <v>1</v>
       </c>
       <c r="M156" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P156" t="s">
         <v>193</v>
       </c>
       <c r="Q156" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -9043,13 +9039,13 @@
         <v>1</v>
       </c>
       <c r="M157" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P157" t="s">
         <v>199</v>
       </c>
       <c r="Q157" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -9092,13 +9088,13 @@
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P158" t="s">
         <v>193</v>
       </c>
       <c r="Q158" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -9141,13 +9137,13 @@
         <v>1</v>
       </c>
       <c r="M159" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P159" t="s">
         <v>195</v>
       </c>
       <c r="Q159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -9196,7 +9192,7 @@
         <v>193</v>
       </c>
       <c r="Q160" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9242,13 +9238,13 @@
         <v>191</v>
       </c>
       <c r="N161" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P161" t="s">
         <v>193</v>
       </c>
       <c r="Q161" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9300,16 +9296,16 @@
         <v>193</v>
       </c>
       <c r="Q162" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S162" t="s">
         <v>132</v>
       </c>
       <c r="T162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="U162" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9355,7 +9351,7 @@
         <v>191</v>
       </c>
       <c r="N163" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P163" t="s">
         <v>129</v>
@@ -9364,7 +9360,7 @@
         <v>191</v>
       </c>
       <c r="R163" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9447,13 +9443,13 @@
         <v>1</v>
       </c>
       <c r="M165" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P165" t="s">
         <v>195</v>
       </c>
       <c r="Q165" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9496,13 +9492,13 @@
         <v>1</v>
       </c>
       <c r="M166" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P166" t="s">
         <v>197</v>
       </c>
       <c r="Q166" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9545,13 +9541,13 @@
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P167" t="s">
         <v>196</v>
       </c>
       <c r="Q167" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9597,7 +9593,7 @@
         <v>191</v>
       </c>
       <c r="N168" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P168" t="s">
         <v>129</v>
@@ -9606,7 +9602,7 @@
         <v>191</v>
       </c>
       <c r="R168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9689,13 +9685,13 @@
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P170" t="s">
         <v>195</v>
       </c>
       <c r="Q170" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9738,13 +9734,13 @@
         <v>1</v>
       </c>
       <c r="M171" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P171" t="s">
         <v>199</v>
       </c>
       <c r="Q171" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.55000000000000004">
@@ -9787,13 +9783,13 @@
         <v>1</v>
       </c>
       <c r="M172" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P172" t="s">
         <v>193</v>
       </c>
       <c r="Q172" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131A0197-C177-4A45-9377-475106F1E0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98792724-4AE4-413E-A58C-A861B6B9B04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="14400" windowHeight="7810" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="229">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -887,6 +887,18 @@
   </si>
   <si>
     <t>Other</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>only_indirect</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>revoke</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1038,12 +1050,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:X172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:X172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:Y172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:Y172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U171">
     <sortCondition ref="A1:A171"/>
   </sortState>
-  <tableColumns count="24">
+  <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{68F464FB-6EAB-4357-81E0-F3A065D812E5}" name="test_name" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{2881E9F4-1C48-436F-A2BA-7A4B3A2E2428}" name="effort"/>
     <tableColumn id="3" xr3:uid="{DB08D917-E1F8-4FDA-B62D-49DD2304FA6D}" name="sequence_number"/>
@@ -1072,6 +1084,7 @@
     <tableColumn id="9" xr3:uid="{960C560C-12FE-4376-9F99-EFAFC7CCC9CA}" name="code-changed_ui_element3"/>
     <tableColumn id="11" xr3:uid="{A890BDC9-BF79-43A8-AA1F-6E7EA04E2953}" name="specific_change(code-changed3)_1"/>
     <tableColumn id="13" xr3:uid="{580284E3-5DD3-4067-BE91-2EA03407652F}" name="specific_change(code-changed3)_2"/>
+    <tableColumn id="14" xr3:uid="{0501D039-39B7-44FE-8E9D-806F597B5FC7}" name="only_indirect"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1394,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC39754-040A-4551-8F70-BC62970F44A3}">
-  <dimension ref="A1:X172"/>
+  <dimension ref="A1:Y172"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="120.5" customWidth="1"/>
@@ -1420,9 +1433,10 @@
     <col min="22" max="22" width="27.9140625" customWidth="1"/>
     <col min="23" max="23" width="33.4140625" customWidth="1"/>
     <col min="24" max="24" width="34.6640625" customWidth="1"/>
+    <col min="25" max="25" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>133</v>
       </c>
@@ -1495,8 +1509,11 @@
       <c r="X1" s="3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y1" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1544,8 +1561,11 @@
       <c r="Q2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1596,8 +1616,11 @@
       <c r="R3" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1648,8 +1671,11 @@
       <c r="R4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1706,8 +1732,11 @@
       <c r="T5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1761,8 +1790,11 @@
       <c r="T6" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1810,8 +1842,11 @@
       <c r="Q7" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -1865,8 +1900,11 @@
       <c r="T8" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1917,8 +1955,11 @@
       <c r="R9" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1957,8 +1998,11 @@
       <c r="L10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1997,8 +2041,11 @@
       <c r="L11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2037,8 +2084,11 @@
       <c r="L12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -2077,8 +2127,11 @@
       <c r="L13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2117,8 +2170,11 @@
       <c r="L14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -2157,8 +2213,11 @@
       <c r="L15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2197,8 +2256,11 @@
       <c r="L16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2252,8 +2314,11 @@
       <c r="T17" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -2304,8 +2369,11 @@
       <c r="R18" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -2347,8 +2415,11 @@
       <c r="Q19" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -2387,8 +2458,11 @@
       <c r="L20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y20" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2427,8 +2501,11 @@
       <c r="L21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2544,11 @@
       <c r="L22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y22" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -2507,8 +2587,11 @@
       <c r="L23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2547,8 +2630,11 @@
       <c r="L24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -2587,8 +2673,11 @@
       <c r="L25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -2627,8 +2716,11 @@
       <c r="L26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y26" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2667,8 +2759,11 @@
       <c r="L27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2707,8 +2802,11 @@
       <c r="L28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y28" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2759,8 +2857,11 @@
       <c r="R29" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -2814,8 +2915,11 @@
       <c r="T30" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -2854,8 +2958,11 @@
       <c r="L31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y31" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -2894,8 +3001,11 @@
       <c r="L32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y32" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -2934,8 +3044,11 @@
       <c r="L33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y33" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -2974,8 +3087,11 @@
       <c r="L34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y34" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -3023,8 +3139,11 @@
       <c r="Q35" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -3072,8 +3191,11 @@
       <c r="Q36" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -3121,8 +3243,11 @@
       <c r="Q37" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -3170,8 +3295,11 @@
       <c r="Q38" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>117</v>
       </c>
@@ -3219,8 +3347,11 @@
       <c r="Q39" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -3259,8 +3390,11 @@
       <c r="L40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>57</v>
       </c>
@@ -3299,8 +3433,11 @@
       <c r="L41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y41" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>16</v>
       </c>
@@ -3354,8 +3491,11 @@
       <c r="R42" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -3409,8 +3549,11 @@
       <c r="R43" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -3464,8 +3607,11 @@
       <c r="R44" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -3504,8 +3650,11 @@
       <c r="L45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y45" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>16</v>
       </c>
@@ -3553,8 +3702,11 @@
       <c r="Q46" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -3602,8 +3754,11 @@
       <c r="Q47" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y47" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -3651,8 +3806,11 @@
       <c r="Q48" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y48" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -3706,8 +3864,11 @@
       <c r="R49" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y49" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -3746,8 +3907,11 @@
       <c r="L50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -3795,8 +3959,11 @@
       <c r="Q51" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -3844,8 +4011,11 @@
       <c r="Q52" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y52" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>103</v>
       </c>
@@ -3899,8 +4069,11 @@
       <c r="T53" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -3951,8 +4124,11 @@
       <c r="R54" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>19</v>
       </c>
@@ -4006,8 +4182,11 @@
       <c r="T55" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -4058,8 +4237,11 @@
       <c r="R56" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -4110,8 +4292,11 @@
       <c r="Q57" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -4159,8 +4344,11 @@
       <c r="Q58" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y58" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -4208,8 +4396,11 @@
       <c r="Q59" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y59" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -4260,8 +4451,11 @@
       <c r="Q60" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -4315,8 +4509,11 @@
       <c r="T61" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>102</v>
       </c>
@@ -4367,8 +4564,11 @@
       <c r="R62" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -4422,8 +4622,11 @@
       <c r="T63" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -4471,8 +4674,11 @@
       <c r="Q64" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -4523,8 +4729,11 @@
       <c r="Q65" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -4563,8 +4772,11 @@
       <c r="L66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y66" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4603,8 +4815,11 @@
       <c r="L67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y67" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4652,8 +4867,11 @@
       <c r="Q68" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y68" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -4692,8 +4910,11 @@
       <c r="L69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y69" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -4732,8 +4953,11 @@
       <c r="L70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y70" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -4781,8 +5005,11 @@
       <c r="Q71" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y71" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -4833,8 +5060,11 @@
       <c r="Q72" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y72" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -4882,8 +5112,11 @@
       <c r="Q73" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -4931,8 +5164,11 @@
       <c r="Q74" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -4980,8 +5216,11 @@
       <c r="Q75" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y75" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -5020,8 +5259,11 @@
       <c r="L76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -5075,8 +5317,11 @@
       <c r="R77" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -5124,8 +5369,11 @@
       <c r="Q78" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -5173,8 +5421,11 @@
       <c r="Q79" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y79" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -5222,8 +5473,11 @@
       <c r="Q80" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y80" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -5277,8 +5531,11 @@
       <c r="R81" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y81" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5317,8 +5574,11 @@
       <c r="L82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -5357,8 +5617,11 @@
       <c r="L83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y83" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -5406,8 +5669,11 @@
       <c r="Q84" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>29</v>
       </c>
@@ -5461,8 +5727,11 @@
       <c r="R85" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -5510,8 +5779,11 @@
       <c r="Q86" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -5559,8 +5831,11 @@
       <c r="Q87" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y87" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -5608,8 +5883,11 @@
       <c r="Q88" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y88" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -5657,8 +5935,11 @@
       <c r="Q89" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y89" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -5712,8 +5993,11 @@
       <c r="R90" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -5767,8 +6051,11 @@
       <c r="R91" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -5822,8 +6109,11 @@
       <c r="R92" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -5862,8 +6152,11 @@
       <c r="L93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y93" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -5902,8 +6195,11 @@
       <c r="L94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y94" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -5951,8 +6247,11 @@
       <c r="Q95" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y95" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -6000,8 +6299,11 @@
       <c r="Q96" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y96" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>80</v>
       </c>
@@ -6055,8 +6357,11 @@
       <c r="R97" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y97" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -6095,8 +6400,11 @@
       <c r="L98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y98" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -6144,8 +6452,11 @@
       <c r="Q99" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y99" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>80</v>
       </c>
@@ -6193,8 +6504,11 @@
       <c r="Q100" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y100" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -6242,8 +6556,11 @@
       <c r="Q101" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -6297,8 +6614,11 @@
       <c r="R102" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -6346,8 +6666,11 @@
       <c r="Q103" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -6395,8 +6718,11 @@
       <c r="Q104" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y104" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -6444,8 +6770,11 @@
       <c r="Q105" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y105" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -6484,8 +6813,11 @@
       <c r="L106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y106" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -6539,8 +6871,11 @@
       <c r="R107" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -6594,8 +6929,11 @@
       <c r="R108" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -6643,8 +6981,11 @@
       <c r="Q109" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y109" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -6692,8 +7033,11 @@
       <c r="Q110" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y110" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -6747,8 +7091,11 @@
       <c r="R111" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y111" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -6802,8 +7149,11 @@
       <c r="R112" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y112" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>64</v>
       </c>
@@ -6842,8 +7192,11 @@
       <c r="L113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y113" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -6891,8 +7244,11 @@
       <c r="Q114" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y114" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>64</v>
       </c>
@@ -6940,8 +7296,11 @@
       <c r="Q115" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y115" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -6989,8 +7348,11 @@
       <c r="Q116" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>81</v>
       </c>
@@ -7038,8 +7400,11 @@
       <c r="Q117" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y117" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>81</v>
       </c>
@@ -7087,8 +7452,11 @@
       <c r="Q118" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y118" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>111</v>
       </c>
@@ -7136,8 +7504,11 @@
       <c r="Q119" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y119" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -7176,8 +7547,11 @@
       <c r="L120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y120" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -7216,8 +7590,11 @@
       <c r="L121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y121" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -7256,8 +7633,11 @@
       <c r="L122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y122" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -7296,8 +7676,11 @@
       <c r="L123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y123" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>85</v>
       </c>
@@ -7348,8 +7731,11 @@
       <c r="R124" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>85</v>
       </c>
@@ -7400,8 +7786,11 @@
       <c r="R125" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>35</v>
       </c>
@@ -7461,8 +7850,11 @@
       <c r="U126" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -7516,8 +7908,11 @@
       <c r="T127" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y127" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>113</v>
       </c>
@@ -7568,8 +7963,11 @@
       <c r="R128" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -7629,8 +8027,11 @@
       <c r="U129" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>107</v>
       </c>
@@ -7678,8 +8079,11 @@
       <c r="Q130" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>100</v>
       </c>
@@ -7727,8 +8131,11 @@
       <c r="Q131" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>66</v>
       </c>
@@ -7792,7 +8199,7 @@
         <v>225</v>
       </c>
       <c r="V132" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="W132" t="s">
         <v>201</v>
@@ -7800,8 +8207,11 @@
       <c r="X132" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -7873,8 +8283,11 @@
       <c r="X133" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y133" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>38</v>
       </c>
@@ -7924,8 +8337,11 @@
       <c r="Q134" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>38</v>
       </c>
@@ -7967,8 +8383,11 @@
       <c r="P135" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>67</v>
       </c>
@@ -8010,8 +8429,11 @@
       <c r="P136" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y136" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>67</v>
       </c>
@@ -8059,8 +8481,11 @@
       <c r="Q137" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y137" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>118</v>
       </c>
@@ -8108,8 +8533,11 @@
       <c r="Q138" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>104</v>
       </c>
@@ -8162,8 +8590,11 @@
       <c r="S139" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>39</v>
       </c>
@@ -8214,8 +8645,11 @@
       <c r="S140" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y140" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -8263,8 +8697,11 @@
       <c r="Q141" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>105</v>
       </c>
@@ -8312,8 +8749,11 @@
       <c r="Q142" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>98</v>
       </c>
@@ -8367,8 +8807,11 @@
       <c r="R143" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>98</v>
       </c>
@@ -8416,8 +8859,11 @@
       <c r="Q144" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>98</v>
       </c>
@@ -8465,8 +8911,11 @@
       <c r="Q145" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y145" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>98</v>
       </c>
@@ -8514,8 +8963,11 @@
       <c r="Q146" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y146" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>90</v>
       </c>
@@ -8569,8 +9021,11 @@
       <c r="R147" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>90</v>
       </c>
@@ -8618,8 +9073,11 @@
       <c r="Q148" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>90</v>
       </c>
@@ -8667,8 +9125,11 @@
       <c r="Q149" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y149" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>90</v>
       </c>
@@ -8716,8 +9177,11 @@
       <c r="Q150" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y150" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -8768,8 +9232,11 @@
       <c r="R151" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -8808,8 +9275,11 @@
       <c r="L152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y152" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>91</v>
       </c>
@@ -8848,8 +9318,11 @@
       <c r="L153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y153" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>106</v>
       </c>
@@ -8900,8 +9373,11 @@
       <c r="R154" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>122</v>
       </c>
@@ -8949,8 +9425,11 @@
       <c r="Q155" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>70</v>
       </c>
@@ -8998,8 +9477,11 @@
       <c r="Q156" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>71</v>
       </c>
@@ -9047,8 +9529,11 @@
       <c r="Q157" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>71</v>
       </c>
@@ -9096,8 +9581,11 @@
       <c r="Q158" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>112</v>
       </c>
@@ -9145,8 +9633,11 @@
       <c r="Q159" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y159" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>108</v>
       </c>
@@ -9194,8 +9685,11 @@
       <c r="Q160" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>109</v>
       </c>
@@ -9246,8 +9740,11 @@
       <c r="Q161" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>109</v>
       </c>
@@ -9307,8 +9804,11 @@
       <c r="U162" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y162" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>42</v>
       </c>
@@ -9362,8 +9862,11 @@
       <c r="R163" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>42</v>
       </c>
@@ -9402,8 +9905,11 @@
       <c r="L164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y164" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>42</v>
       </c>
@@ -9451,8 +9957,11 @@
       <c r="Q165" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>42</v>
       </c>
@@ -9500,8 +10009,11 @@
       <c r="Q166" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y166" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>42</v>
       </c>
@@ -9549,8 +10061,11 @@
       <c r="Q167" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y167" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>42</v>
       </c>
@@ -9604,8 +10119,11 @@
       <c r="R168" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y168" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -9644,8 +10162,11 @@
       <c r="L169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y169" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>42</v>
       </c>
@@ -9693,8 +10214,11 @@
       <c r="Q170" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y170" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>49</v>
       </c>
@@ -9742,8 +10266,11 @@
       <c r="Q171" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>116</v>
       </c>
@@ -9790,6 +10317,9 @@
       </c>
       <c r="Q172" t="s">
         <v>213</v>
+      </c>
+      <c r="Y172">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98792724-4AE4-413E-A58C-A861B6B9B04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0473878-883D-4046-8006-4A82EDFB70B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="229">
   <si>
     <t>1042-1043</t>
     <phoneticPr fontId="1"/>
@@ -1051,7 +1051,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:Y172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:Y172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
+  <autoFilter ref="A1:Y172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="cursor_travel_distance"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U171">
     <sortCondition ref="A1:A171"/>
   </sortState>
@@ -1736,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1959,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2002,7 +2013,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2045,7 +2056,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2088,7 +2099,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>101</v>
       </c>
@@ -2131,7 +2142,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2174,7 +2185,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -2217,7 +2228,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2373,7 +2384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -2419,7 +2430,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -2462,7 +2473,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2505,7 +2516,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -2548,7 +2559,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -2591,7 +2602,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
@@ -2634,7 +2645,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -2677,7 +2688,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>56</v>
       </c>
@@ -2720,7 +2731,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -2763,7 +2774,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2919,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>123</v>
       </c>
@@ -2962,7 +2973,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>123</v>
       </c>
@@ -3005,7 +3016,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -3048,7 +3059,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>53</v>
       </c>
@@ -3351,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -3394,7 +3405,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>57</v>
       </c>
@@ -3611,7 +3622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>16</v>
       </c>
@@ -3706,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>16</v>
       </c>
@@ -3758,7 +3769,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -3810,7 +3821,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>16</v>
       </c>
@@ -3868,7 +3879,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -3911,7 +3922,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>16</v>
       </c>
@@ -3963,7 +3974,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -4292,11 +4303,11 @@
       <c r="Q57" t="s">
         <v>225</v>
       </c>
-      <c r="Y57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -4348,7 +4359,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -4400,7 +4411,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -4729,11 +4740,11 @@
       <c r="Q65" t="s">
         <v>225</v>
       </c>
-      <c r="Y65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y65" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -4776,7 +4787,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4819,7 +4830,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4871,7 +4882,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -4914,7 +4925,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -4957,7 +4968,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -5168,7 +5179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -5220,7 +5231,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -5373,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -5425,7 +5436,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -5477,7 +5488,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -5535,7 +5546,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -5578,7 +5589,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -5621,7 +5632,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -5783,7 +5794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -5835,7 +5846,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>29</v>
       </c>
@@ -5887,7 +5898,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>79</v>
       </c>
@@ -6113,7 +6124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -6156,7 +6167,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -6199,7 +6210,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -6251,7 +6262,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -6303,7 +6314,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>80</v>
       </c>
@@ -6361,7 +6372,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -6404,7 +6415,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -6456,7 +6467,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>80</v>
       </c>
@@ -6670,7 +6681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -6722,7 +6733,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -6774,7 +6785,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -6933,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -6985,7 +6996,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>97</v>
       </c>
@@ -7037,7 +7048,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>33</v>
       </c>
@@ -7095,7 +7106,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>33</v>
       </c>
@@ -7153,7 +7164,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>64</v>
       </c>
@@ -7196,7 +7207,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -7248,7 +7259,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>64</v>
       </c>
@@ -7352,7 +7363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>81</v>
       </c>
@@ -7404,7 +7415,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>81</v>
       </c>
@@ -7456,7 +7467,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>111</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -7551,7 +7562,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -7594,7 +7605,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -7637,7 +7648,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -7854,7 +7865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>85</v>
       </c>
@@ -8207,11 +8218,11 @@
       <c r="X132" t="s">
         <v>203</v>
       </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y132" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>66</v>
       </c>
@@ -8383,11 +8394,14 @@
       <c r="P135" t="s">
         <v>222</v>
       </c>
-      <c r="Y135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q135" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>67</v>
       </c>
@@ -8433,7 +8447,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>67</v>
       </c>
@@ -8594,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>39</v>
       </c>
@@ -8863,7 +8877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>98</v>
       </c>
@@ -8915,7 +8929,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>98</v>
       </c>
@@ -9077,7 +9091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>90</v>
       </c>
@@ -9129,7 +9143,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>90</v>
       </c>
@@ -9236,7 +9250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -9279,7 +9293,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>91</v>
       </c>
@@ -9585,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>112</v>
       </c>
@@ -9744,7 +9758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>109</v>
       </c>
@@ -9866,7 +9880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>42</v>
       </c>
@@ -9961,7 +9975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>42</v>
       </c>
@@ -10013,7 +10027,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>42</v>
       </c>
@@ -10065,7 +10079,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>42</v>
       </c>
@@ -10123,7 +10137,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -10166,7 +10180,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>42</v>
       </c>

--- a/Data/Timeoff/timeoff.xlsx
+++ b/Data/Timeoff/timeoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ESEM2026\Data\Timeoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0473878-883D-4046-8006-4A82EDFB70B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799E06AD-556C-4E38-B570-E35E861F2C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{76F834DE-5EFC-4D6B-9741-493A547AC4EA}"/>
   </bookViews>
@@ -542,10 +542,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>dloc</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>lines_added</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -899,6 +895,10 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>changed_lines</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1051,18 +1051,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}" name="テーブル1" displayName="テーブル1" ref="A1:Y172" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:Y172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="cursor_travel_distance"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="11">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y172" xr:uid="{9B58A573-DDAE-4BA0-9BCD-822DA6AE140A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U171">
     <sortCondition ref="A1:A171"/>
   </sortState>
@@ -1070,7 +1059,7 @@
     <tableColumn id="1" xr3:uid="{68F464FB-6EAB-4357-81E0-F3A065D812E5}" name="test_name" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{2881E9F4-1C48-436F-A2BA-7A4B3A2E2428}" name="effort"/>
     <tableColumn id="3" xr3:uid="{DB08D917-E1F8-4FDA-B62D-49DD2304FA6D}" name="sequence_number"/>
-    <tableColumn id="4" xr3:uid="{5FF37A87-22AB-4D95-9DE3-5802EAC09693}" name="dloc">
+    <tableColumn id="4" xr3:uid="{5FF37A87-22AB-4D95-9DE3-5802EAC09693}" name="changed_lines">
       <calculatedColumnFormula>E2+F2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{E1819659-06C2-42BC-A033-8738ECB33D1B}" name="lines_added" dataDxfId="2"/>
@@ -1458,70 +1447,70 @@
         <v>135</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="V1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="Y1" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -1529,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
@@ -1545,7 +1534,7 @@
         <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H2">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1558,19 +1547,19 @@
         <v>910.35487585885903</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y2">
         <v>1</v>
@@ -1581,7 +1570,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
         <v>43</v>
@@ -1597,7 +1586,7 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H3">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1610,22 +1599,22 @@
         <v>726.16783091409297</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P3" t="s">
         <v>124</v>
       </c>
       <c r="Q3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y3">
         <v>1</v>
@@ -1636,7 +1625,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -1652,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1665,22 +1654,22 @@
         <v>723.54111845857994</v>
       </c>
       <c r="K4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P4" t="s">
         <v>125</v>
       </c>
       <c r="Q4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y4">
         <v>1</v>
@@ -1691,7 +1680,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -1707,7 +1696,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H5">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1720,39 +1709,39 @@
         <v>723.54111845857994</v>
       </c>
       <c r="K5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P5" t="s">
         <v>125</v>
       </c>
       <c r="Q5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1768,7 +1757,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H6">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1781,28 +1770,28 @@
         <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P6" t="s">
         <v>125</v>
       </c>
       <c r="Q6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -1810,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
@@ -1826,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1839,19 +1828,19 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y7">
         <v>1</v>
@@ -1862,7 +1851,7 @@
         <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
         <v>47</v>
@@ -1878,7 +1867,7 @@
         <v>4992</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1891,25 +1880,25 @@
         <v>873.212459828649</v>
       </c>
       <c r="K8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y8">
         <v>1</v>
@@ -1920,7 +1909,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
         <v>43</v>
@@ -1936,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H9">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -1949,33 +1938,33 @@
         <v>1013.01776884712</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P9" t="s">
         <v>126</v>
       </c>
       <c r="Q9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -1991,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H10">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2004,21 +1993,21 @@
         <v>1013.61333850734</v>
       </c>
       <c r="K10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="Y10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
@@ -2034,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H11">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2047,21 +2036,21 @@
         <v>510</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -2077,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H12">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2090,21 +2079,21 @@
         <v>439</v>
       </c>
       <c r="K12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
         <v>45</v>
@@ -2120,7 +2109,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H13">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2133,21 +2122,21 @@
         <v>1992.3122787372499</v>
       </c>
       <c r="K13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -2163,7 +2152,7 @@
         <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H14">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2176,21 +2165,21 @@
         <v>2495.29425930769</v>
       </c>
       <c r="K14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -2206,7 +2195,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H15">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2219,21 +2208,21 @@
         <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -2249,7 +2238,7 @@
         <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H16">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2262,13 +2251,13 @@
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -2276,7 +2265,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -2292,7 +2281,7 @@
         <v>297</v>
       </c>
       <c r="G17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2305,25 +2294,25 @@
         <v>1259.1642187299201</v>
       </c>
       <c r="K17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y17">
         <v>1</v>
@@ -2334,7 +2323,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" t="s">
         <v>1</v>
@@ -2350,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H18">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2363,33 +2352,33 @@
         <v>1279.5560215426799</v>
       </c>
       <c r="K18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P18" t="s">
         <v>127</v>
       </c>
       <c r="Q18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
         <v>51</v>
@@ -2405,7 +2394,7 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H19">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2418,24 +2407,24 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
         <v>51</v>
@@ -2451,7 +2440,7 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H20">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2464,21 +2453,21 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
         <v>52</v>
@@ -2494,7 +2483,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H21">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2507,21 +2496,21 @@
         <v>1043.76719125258</v>
       </c>
       <c r="K21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22" t="s">
         <v>52</v>
@@ -2537,7 +2526,7 @@
         <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H22">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2550,21 +2539,21 @@
         <v>1043.76719125258</v>
       </c>
       <c r="K22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
         <v>51</v>
@@ -2580,7 +2569,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H23">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2593,21 +2582,21 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
         <v>51</v>
@@ -2623,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H24">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2636,21 +2625,21 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="Y24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
         <v>52</v>
@@ -2666,7 +2655,7 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H25">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2679,21 +2668,21 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="Y25" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
         <v>52</v>
@@ -2709,7 +2698,7 @@
         <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H26">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2722,21 +2711,21 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="Y26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
         <v>2</v>
@@ -2752,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H27">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2765,21 +2754,21 @@
         <v>1046.9269094660999</v>
       </c>
       <c r="K27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="Y27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
         <v>2</v>
@@ -2795,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H28">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2808,13 +2797,13 @@
         <v>114</v>
       </c>
       <c r="K28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="Y28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -2822,7 +2811,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -2838,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H29">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2851,22 +2840,22 @@
         <v>331.86895003901702</v>
       </c>
       <c r="K29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L29">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P29" t="s">
         <v>128</v>
       </c>
       <c r="Q29" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y29">
         <v>1</v>
@@ -2877,7 +2866,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
         <v>1</v>
@@ -2893,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H30">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2906,36 +2895,36 @@
         <v>368.31644003492403</v>
       </c>
       <c r="K30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L30">
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P30" t="s">
         <v>128</v>
       </c>
       <c r="Q30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>123</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
         <v>54</v>
@@ -2951,7 +2940,7 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H31">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -2964,21 +2953,21 @@
         <v>1992.3122787372499</v>
       </c>
       <c r="K31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="Y31" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>55</v>
@@ -2994,7 +2983,7 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H32">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3007,21 +2996,21 @@
         <v>2495.29425930769</v>
       </c>
       <c r="K32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="Y32" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
         <v>54</v>
@@ -3037,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H33">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3050,21 +3039,21 @@
         <v>3</v>
       </c>
       <c r="K33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="Y33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
         <v>55</v>
@@ -3080,7 +3069,7 @@
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H34">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3093,13 +3082,13 @@
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="Y34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -3107,7 +3096,7 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
@@ -3123,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H35">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3136,19 +3125,19 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L35">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y35">
         <v>1</v>
@@ -3159,7 +3148,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
         <v>1</v>
@@ -3175,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H36">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3188,19 +3177,19 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y36">
         <v>1</v>
@@ -3211,7 +3200,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C37" t="s">
         <v>1</v>
@@ -3227,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H37">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3240,19 +3229,19 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L37">
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y37">
         <v>1</v>
@@ -3263,7 +3252,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
         <v>1</v>
@@ -3279,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H38">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3292,19 +3281,19 @@
         <v>610.73480333120006</v>
       </c>
       <c r="K38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L38">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y38">
         <v>1</v>
@@ -3315,7 +3304,7 @@
         <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
         <v>58</v>
@@ -3331,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H39">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3344,30 +3333,30 @@
         <v>831.87018217988702</v>
       </c>
       <c r="K39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L39">
         <v>1</v>
       </c>
       <c r="M39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
         <v>59</v>
@@ -3383,7 +3372,7 @@
         <v>119</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H40">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3396,21 +3385,21 @@
         <v>809.35035676769803</v>
       </c>
       <c r="K40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="Y40" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>57</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
         <v>60</v>
@@ -3426,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H41">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3439,13 +3428,13 @@
         <v>831.87018217988702</v>
       </c>
       <c r="K41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="Y41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -3453,7 +3442,7 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C42" t="s">
         <v>3</v>
@@ -3469,7 +3458,7 @@
         <v>297</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H42">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3482,25 +3471,25 @@
         <v>886.76898739733599</v>
       </c>
       <c r="K42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L42">
         <v>1</v>
       </c>
       <c r="M42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P42" t="s">
         <v>129</v>
       </c>
       <c r="Q42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -3511,7 +3500,7 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
         <v>3</v>
@@ -3527,7 +3516,7 @@
         <v>297</v>
       </c>
       <c r="G43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H43">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3540,25 +3529,25 @@
         <v>886.76898739733599</v>
       </c>
       <c r="K43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L43">
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P43" t="s">
         <v>129</v>
       </c>
       <c r="Q43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -3569,7 +3558,7 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C44" t="s">
         <v>3</v>
@@ -3585,7 +3574,7 @@
         <v>297</v>
       </c>
       <c r="G44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H44">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3598,36 +3587,36 @@
         <v>886.76898739733599</v>
       </c>
       <c r="K44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L44">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P44" t="s">
         <v>129</v>
       </c>
       <c r="Q44" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -3643,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H45">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3656,13 +3645,13 @@
         <v>887.68793537055103</v>
       </c>
       <c r="K45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="Y45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -3670,7 +3659,7 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
@@ -3686,7 +3675,7 @@
         <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H46">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3699,30 +3688,30 @@
         <v>887.28906064045304</v>
       </c>
       <c r="K46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L46">
         <v>1</v>
       </c>
       <c r="M46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
         <v>77</v>
@@ -3738,7 +3727,7 @@
         <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H47">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3751,30 +3740,30 @@
         <v>581</v>
       </c>
       <c r="K47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L47">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y47" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
         <v>78</v>
@@ -3790,7 +3779,7 @@
         <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H48">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3803,30 +3792,30 @@
         <v>781</v>
       </c>
       <c r="K48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L48">
         <v>1</v>
       </c>
       <c r="M48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y48" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -3842,7 +3831,7 @@
         <v>297</v>
       </c>
       <c r="G49" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H49">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3855,36 +3844,36 @@
         <v>762</v>
       </c>
       <c r="K49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L49">
         <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P49" t="s">
         <v>129</v>
       </c>
       <c r="Q49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y49" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
         <v>2</v>
@@ -3900,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H50">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3913,21 +3902,21 @@
         <v>761</v>
       </c>
       <c r="K50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="Y50" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -3943,7 +3932,7 @@
         <v>18</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H51">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -3956,30 +3945,30 @@
         <v>842</v>
       </c>
       <c r="K51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L51">
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -3995,7 +3984,7 @@
         <v>18</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H52">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4008,22 +3997,22 @@
         <v>842</v>
       </c>
       <c r="K52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L52">
         <v>1</v>
       </c>
       <c r="M52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -4031,7 +4020,7 @@
         <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s">
         <v>3</v>
@@ -4047,7 +4036,7 @@
         <v>297</v>
       </c>
       <c r="G53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H53">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4060,25 +4049,25 @@
         <v>1070.92001517789</v>
       </c>
       <c r="K53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L53">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S53" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y53">
         <v>1</v>
@@ -4089,7 +4078,7 @@
         <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
         <v>1</v>
@@ -4105,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H54">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4118,22 +4107,22 @@
         <v>1103.7909566187</v>
       </c>
       <c r="K54" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L54">
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P54" t="s">
         <v>127</v>
       </c>
       <c r="Q54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y54">
         <v>1</v>
@@ -4144,7 +4133,7 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
@@ -4160,7 +4149,7 @@
         <v>297</v>
       </c>
       <c r="G55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H55">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4173,25 +4162,25 @@
         <v>1225.2518849257999</v>
       </c>
       <c r="K55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L55">
         <v>1</v>
       </c>
       <c r="M55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y55">
         <v>1</v>
@@ -4202,7 +4191,7 @@
         <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C56" t="s">
         <v>1</v>
@@ -4218,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H56">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4231,22 +4220,22 @@
         <v>1267.9611358135101</v>
       </c>
       <c r="K56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L56">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P56" t="s">
         <v>127</v>
       </c>
       <c r="Q56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y56">
         <v>1</v>
@@ -4257,7 +4246,7 @@
         <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
@@ -4273,7 +4262,7 @@
         <v>4391</v>
       </c>
       <c r="G57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H57">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4286,33 +4275,33 @@
         <v>1064.42707594273</v>
       </c>
       <c r="K57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L57">
         <v>1</v>
       </c>
       <c r="M57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y57" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
         <v>75</v>
@@ -4328,7 +4317,7 @@
         <v>21</v>
       </c>
       <c r="G58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H58">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4341,30 +4330,30 @@
         <v>624</v>
       </c>
       <c r="K58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L58">
         <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y58" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>21</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
         <v>76</v>
@@ -4380,7 +4369,7 @@
         <v>59</v>
       </c>
       <c r="G59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H59">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4393,30 +4382,30 @@
         <v>824</v>
       </c>
       <c r="K59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L59">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y59" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
@@ -4432,7 +4421,7 @@
         <v>4391</v>
       </c>
       <c r="G60" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H60">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4445,25 +4434,25 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L60">
         <v>1</v>
       </c>
       <c r="M60" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N60" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -4471,7 +4460,7 @@
         <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
@@ -4487,7 +4476,7 @@
         <v>297</v>
       </c>
       <c r="G61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H61">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4500,25 +4489,25 @@
         <v>1078.8150907361201</v>
       </c>
       <c r="K61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L61">
         <v>1</v>
       </c>
       <c r="M61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S61" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y61">
         <v>1</v>
@@ -4529,7 +4518,7 @@
         <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
@@ -4545,7 +4534,7 @@
         <v>1</v>
       </c>
       <c r="G62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H62">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4558,22 +4547,22 @@
         <v>1093.0370533518001</v>
       </c>
       <c r="K62" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L62">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P62" t="s">
         <v>127</v>
       </c>
       <c r="Q62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y62">
         <v>1</v>
@@ -4584,7 +4573,7 @@
         <v>23</v>
       </c>
       <c r="B63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
@@ -4600,7 +4589,7 @@
         <v>297</v>
       </c>
       <c r="G63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H63">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4613,25 +4602,25 @@
         <v>994.73463798140597</v>
       </c>
       <c r="K63" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L63">
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S63" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y63">
         <v>1</v>
@@ -4642,7 +4631,7 @@
         <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
         <v>17</v>
@@ -4658,7 +4647,7 @@
         <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H64">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4671,19 +4660,19 @@
         <v>1007.29191399514</v>
       </c>
       <c r="K64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L64">
         <v>1</v>
       </c>
       <c r="M64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P64" t="s">
         <v>127</v>
       </c>
       <c r="Q64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y64">
         <v>1</v>
@@ -4694,7 +4683,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C65" t="s">
         <v>24</v>
@@ -4710,7 +4699,7 @@
         <v>4391</v>
       </c>
       <c r="G65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H65">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4723,33 +4712,33 @@
         <v>1007.29191399514</v>
       </c>
       <c r="K65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L65">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y65" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C66" t="s">
         <v>61</v>
@@ -4765,7 +4754,7 @@
         <v>52</v>
       </c>
       <c r="G66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H66">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4778,21 +4767,21 @@
         <v>452.95143227502803</v>
       </c>
       <c r="K66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="Y66" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" t="s">
         <v>62</v>
@@ -4808,7 +4797,7 @@
         <v>7</v>
       </c>
       <c r="G67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H67">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4821,21 +4810,21 @@
         <v>427.61782002157003</v>
       </c>
       <c r="K67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="Y67" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" t="s">
         <v>75</v>
@@ -4851,7 +4840,7 @@
         <v>21</v>
       </c>
       <c r="G68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H68">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4864,30 +4853,30 @@
         <v>722</v>
       </c>
       <c r="K68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L68">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y68" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
         <v>99</v>
@@ -4903,7 +4892,7 @@
         <v>52</v>
       </c>
       <c r="G69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H69">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4916,21 +4905,21 @@
         <v>696</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="Y69" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" t="s">
         <v>62</v>
@@ -4946,7 +4935,7 @@
         <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H70">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -4959,21 +4948,21 @@
         <v>722</v>
       </c>
       <c r="K70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="Y70" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C71" t="s">
         <v>76</v>
@@ -4989,7 +4978,7 @@
         <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H71">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5002,30 +4991,30 @@
         <v>922</v>
       </c>
       <c r="K71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L71">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q71" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y71" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
         <v>24</v>
@@ -5041,7 +5030,7 @@
         <v>4391</v>
       </c>
       <c r="G72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H72">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5054,25 +5043,25 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L72">
         <v>1</v>
       </c>
       <c r="M72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q72" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -5080,7 +5069,7 @@
         <v>110</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C73" t="s">
         <v>26</v>
@@ -5096,7 +5085,7 @@
         <v>18</v>
       </c>
       <c r="G73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H73">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5109,19 +5098,19 @@
         <v>2964.0694750887001</v>
       </c>
       <c r="K73" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L73">
         <v>1</v>
       </c>
       <c r="M73" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y73">
         <v>1</v>
@@ -5132,7 +5121,7 @@
         <v>110</v>
       </c>
       <c r="B74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
         <v>26</v>
@@ -5148,7 +5137,7 @@
         <v>18</v>
       </c>
       <c r="G74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H74">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5161,30 +5150,30 @@
         <v>2964.0694750887001</v>
       </c>
       <c r="K74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L74">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
         <v>26</v>
@@ -5200,7 +5189,7 @@
         <v>18</v>
       </c>
       <c r="G75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H75">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5213,30 +5202,30 @@
         <v>1935</v>
       </c>
       <c r="K75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L75">
         <v>1</v>
       </c>
       <c r="M75" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y75" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>28</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
         <v>31</v>
@@ -5252,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H76">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5265,13 +5254,13 @@
         <v>1640.3041251826401</v>
       </c>
       <c r="K76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="Y76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -5279,7 +5268,7 @@
         <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -5295,7 +5284,7 @@
         <v>297</v>
       </c>
       <c r="G77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H77">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5308,25 +5297,25 @@
         <v>1638.48682081575</v>
       </c>
       <c r="K77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L77">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N77" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P77" t="s">
         <v>129</v>
       </c>
       <c r="Q77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y77">
         <v>0</v>
@@ -5337,7 +5326,7 @@
         <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C78" t="s">
         <v>26</v>
@@ -5353,7 +5342,7 @@
         <v>18</v>
       </c>
       <c r="G78" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H78">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5366,30 +5355,30 @@
         <v>1699.20763866736</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L78">
         <v>1</v>
       </c>
       <c r="M78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q78" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>28</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" t="s">
         <v>75</v>
@@ -5405,7 +5394,7 @@
         <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H79">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5418,30 +5407,30 @@
         <v>662</v>
       </c>
       <c r="K79" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L79">
         <v>1</v>
       </c>
       <c r="M79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y79" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>28</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C80" t="s">
         <v>76</v>
@@ -5457,7 +5446,7 @@
         <v>59</v>
       </c>
       <c r="G80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H80">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5470,30 +5459,30 @@
         <v>862</v>
       </c>
       <c r="K80" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L80">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y80" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>28</v>
       </c>
       <c r="B81" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C81" t="s">
         <v>18</v>
@@ -5509,7 +5498,7 @@
         <v>297</v>
       </c>
       <c r="G81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H81">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5522,36 +5511,36 @@
         <v>824</v>
       </c>
       <c r="K81" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L81">
         <v>1</v>
       </c>
       <c r="M81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P81" t="s">
         <v>129</v>
       </c>
       <c r="Q81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y81" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>28</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C82" t="s">
         <v>31</v>
@@ -5567,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H82">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5580,21 +5569,21 @@
         <v>823</v>
       </c>
       <c r="K82" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="Y82" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
         <v>17</v>
@@ -5610,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H83">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5623,21 +5612,21 @@
         <v>1640.3041251826401</v>
       </c>
       <c r="K83" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="Y83" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C84" t="s">
         <v>26</v>
@@ -5653,7 +5642,7 @@
         <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H84">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5666,22 +5655,22 @@
         <v>984</v>
       </c>
       <c r="K84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L84">
         <v>1</v>
       </c>
       <c r="M84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q84" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y84" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -5689,7 +5678,7 @@
         <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
@@ -5705,7 +5694,7 @@
         <v>297</v>
       </c>
       <c r="G85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H85">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5718,25 +5707,25 @@
         <v>714.53621321805599</v>
       </c>
       <c r="K85" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L85">
         <v>1</v>
       </c>
       <c r="M85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N85" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P85" t="s">
         <v>129</v>
       </c>
       <c r="Q85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R85" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y85">
         <v>0</v>
@@ -5747,7 +5736,7 @@
         <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C86" t="s">
         <v>26</v>
@@ -5763,7 +5752,7 @@
         <v>18</v>
       </c>
       <c r="G86" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H86">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5776,30 +5765,30 @@
         <v>777.13383660731097</v>
       </c>
       <c r="K86" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L86">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
         <v>75</v>
@@ -5815,7 +5804,7 @@
         <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H87">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5828,30 +5817,30 @@
         <v>770</v>
       </c>
       <c r="K87" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L87">
         <v>1</v>
       </c>
       <c r="M87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P87" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q87" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y87" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C88" t="s">
         <v>76</v>
@@ -5867,7 +5856,7 @@
         <v>59</v>
       </c>
       <c r="G88" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H88">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5880,30 +5869,30 @@
         <v>970</v>
       </c>
       <c r="K88" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L88">
         <v>1</v>
       </c>
       <c r="M88" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q88" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y88" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
         <v>26</v>
@@ -5919,7 +5908,7 @@
         <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H89">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5932,22 +5921,22 @@
         <v>1022</v>
       </c>
       <c r="K89" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L89">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P89" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q89" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -5955,7 +5944,7 @@
         <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
@@ -5971,7 +5960,7 @@
         <v>297</v>
       </c>
       <c r="G90" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H90">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -5984,25 +5973,25 @@
         <v>886.48839583435301</v>
       </c>
       <c r="K90" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L90">
         <v>1</v>
       </c>
       <c r="M90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N90" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P90" t="s">
         <v>129</v>
       </c>
       <c r="Q90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y90">
         <v>0</v>
@@ -6013,7 +6002,7 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
@@ -6029,7 +6018,7 @@
         <v>297</v>
       </c>
       <c r="G91" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H91">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6042,25 +6031,25 @@
         <v>886.48839583435301</v>
       </c>
       <c r="K91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L91">
         <v>1</v>
       </c>
       <c r="M91" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N91" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P91" t="s">
         <v>129</v>
       </c>
       <c r="Q91" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R91" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y91">
         <v>0</v>
@@ -6071,7 +6060,7 @@
         <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -6087,7 +6076,7 @@
         <v>297</v>
       </c>
       <c r="G92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H92">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6100,36 +6089,36 @@
         <v>886.48839583435301</v>
       </c>
       <c r="K92" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L92">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N92" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P92" t="s">
         <v>129</v>
       </c>
       <c r="Q92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R92" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
         <v>2</v>
@@ -6145,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H93">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6158,21 +6147,21 @@
         <v>887.36891085317495</v>
       </c>
       <c r="K93" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="Y93" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
@@ -6188,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H94">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6201,21 +6190,21 @@
         <v>887.36891085317495</v>
       </c>
       <c r="K94" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="Y94" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>30</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
         <v>75</v>
@@ -6231,7 +6220,7 @@
         <v>21</v>
       </c>
       <c r="G95" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H95">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6244,30 +6233,30 @@
         <v>591</v>
       </c>
       <c r="K95" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L95">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P95" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q95" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y95" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
         <v>76</v>
@@ -6283,7 +6272,7 @@
         <v>59</v>
       </c>
       <c r="G96" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H96">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6296,30 +6285,30 @@
         <v>791</v>
       </c>
       <c r="K96" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L96">
         <v>1</v>
       </c>
       <c r="M96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P96" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q96" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y96" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>80</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
@@ -6335,7 +6324,7 @@
         <v>297</v>
       </c>
       <c r="G97" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H97">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6348,36 +6337,36 @@
         <v>734</v>
       </c>
       <c r="K97" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L97">
         <v>1</v>
       </c>
       <c r="M97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P97" t="s">
         <v>129</v>
       </c>
       <c r="Q97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y97" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>80</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
@@ -6393,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H98">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6406,21 +6395,21 @@
         <v>733</v>
       </c>
       <c r="K98" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="Y98" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>30</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C99" t="s">
         <v>26</v>
@@ -6436,7 +6425,7 @@
         <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H99">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6449,30 +6438,30 @@
         <v>842</v>
       </c>
       <c r="K99" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L99">
         <v>1</v>
       </c>
       <c r="M99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P99" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q99" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y99" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>80</v>
       </c>
       <c r="B100" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C100" t="s">
         <v>26</v>
@@ -6488,7 +6477,7 @@
         <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H100">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6501,22 +6490,22 @@
         <v>842</v>
       </c>
       <c r="K100" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L100">
         <v>1</v>
       </c>
       <c r="M100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P100" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q100" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y100" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -6524,7 +6513,7 @@
         <v>30</v>
       </c>
       <c r="B101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C101" t="s">
         <v>27</v>
@@ -6540,7 +6529,7 @@
         <v>18</v>
       </c>
       <c r="G101" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H101">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6553,19 +6542,19 @@
         <v>887.28906064045304</v>
       </c>
       <c r="K101" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L101">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q101" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y101">
         <v>1</v>
@@ -6576,7 +6565,7 @@
         <v>32</v>
       </c>
       <c r="B102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C102" t="s">
         <v>18</v>
@@ -6592,7 +6581,7 @@
         <v>297</v>
       </c>
       <c r="G102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H102">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6605,25 +6594,25 @@
         <v>669.30561031564605</v>
       </c>
       <c r="K102" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L102">
         <v>1</v>
       </c>
       <c r="M102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N102" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P102" t="s">
         <v>129</v>
       </c>
       <c r="Q102" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R102" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y102">
         <v>0</v>
@@ -6634,7 +6623,7 @@
         <v>32</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C103" t="s">
         <v>26</v>
@@ -6650,7 +6639,7 @@
         <v>18</v>
       </c>
       <c r="G103" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H103">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6663,30 +6652,30 @@
         <v>733.70975187740203</v>
       </c>
       <c r="K103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L103">
         <v>1</v>
       </c>
       <c r="M103" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P103" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q103" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C104" t="s">
         <v>75</v>
@@ -6702,7 +6691,7 @@
         <v>21</v>
       </c>
       <c r="G104" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H104">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6715,30 +6704,30 @@
         <v>770</v>
       </c>
       <c r="K104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L104">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q104" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y104" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>32</v>
       </c>
       <c r="B105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C105" t="s">
         <v>76</v>
@@ -6754,7 +6743,7 @@
         <v>59</v>
       </c>
       <c r="G105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H105">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6767,30 +6756,30 @@
         <v>970</v>
       </c>
       <c r="K105" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L105">
         <v>1</v>
       </c>
       <c r="M105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P105" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q105" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y105" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C106" t="s">
         <v>2</v>
@@ -6806,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="G106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H106">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6819,13 +6808,13 @@
         <v>864.37479502139797</v>
       </c>
       <c r="K106" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="Y106" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -6833,7 +6822,7 @@
         <v>33</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C107" t="s">
         <v>18</v>
@@ -6849,7 +6838,7 @@
         <v>297</v>
       </c>
       <c r="G107" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H107">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6862,25 +6851,25 @@
         <v>864.43503002847297</v>
       </c>
       <c r="K107" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L107">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P107" t="s">
         <v>129</v>
       </c>
       <c r="Q107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R107" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y107">
         <v>0</v>
@@ -6891,7 +6880,7 @@
         <v>33</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
@@ -6907,7 +6896,7 @@
         <v>297</v>
       </c>
       <c r="G108" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H108">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6920,36 +6909,36 @@
         <v>864.43503002847297</v>
       </c>
       <c r="K108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L108">
         <v>1</v>
       </c>
       <c r="M108" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P108" t="s">
         <v>129</v>
       </c>
       <c r="Q108" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>33</v>
       </c>
       <c r="B109" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C109" t="s">
         <v>77</v>
@@ -6965,7 +6954,7 @@
         <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H109">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -6978,30 +6967,30 @@
         <v>662</v>
       </c>
       <c r="K109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L109">
         <v>1</v>
       </c>
       <c r="M109" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P109" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q109" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y109" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>97</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
         <v>76</v>
@@ -7017,7 +7006,7 @@
         <v>59</v>
       </c>
       <c r="G110" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H110">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7030,30 +7019,30 @@
         <v>862</v>
       </c>
       <c r="K110" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L110">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P110" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q110" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y110" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
@@ -7069,7 +7058,7 @@
         <v>297</v>
       </c>
       <c r="G111" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H111">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7082,36 +7071,36 @@
         <v>824</v>
       </c>
       <c r="K111" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L111">
         <v>1</v>
       </c>
       <c r="M111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N111" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P111" t="s">
         <v>129</v>
       </c>
       <c r="Q111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R111" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y111" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
@@ -7127,7 +7116,7 @@
         <v>297</v>
       </c>
       <c r="G112" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H112">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7140,36 +7129,36 @@
         <v>824</v>
       </c>
       <c r="K112" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L112">
         <v>1</v>
       </c>
       <c r="M112" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N112" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P112" t="s">
         <v>129</v>
       </c>
       <c r="Q112" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R112" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y112" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>64</v>
       </c>
       <c r="B113" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C113" t="s">
         <v>31</v>
@@ -7185,7 +7174,7 @@
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H113">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7198,21 +7187,21 @@
         <v>823</v>
       </c>
       <c r="K113" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="Y113" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C114" t="s">
         <v>26</v>
@@ -7228,7 +7217,7 @@
         <v>18</v>
       </c>
       <c r="G114" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H114">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7241,30 +7230,30 @@
         <v>913</v>
       </c>
       <c r="K114" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L114">
         <v>1</v>
       </c>
       <c r="M114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y114" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>64</v>
       </c>
       <c r="B115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C115" t="s">
         <v>26</v>
@@ -7280,7 +7269,7 @@
         <v>18</v>
       </c>
       <c r="G115" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H115">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7293,22 +7282,22 @@
         <v>913</v>
       </c>
       <c r="K115" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L115">
         <v>1</v>
       </c>
       <c r="M115" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q115" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y115" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -7316,7 +7305,7 @@
         <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
         <v>26</v>
@@ -7332,7 +7321,7 @@
         <v>18</v>
       </c>
       <c r="G116" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H116">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7345,30 +7334,30 @@
         <v>733.70975187740203</v>
       </c>
       <c r="K116" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L116">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q116" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>81</v>
       </c>
       <c r="B117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C117" t="s">
         <v>26</v>
@@ -7384,7 +7373,7 @@
         <v>18</v>
       </c>
       <c r="G117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H117">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7397,30 +7386,30 @@
         <v>1131</v>
       </c>
       <c r="K117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L117">
         <v>1</v>
       </c>
       <c r="M117" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q117" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y117" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>81</v>
       </c>
       <c r="B118" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C118" t="s">
         <v>26</v>
@@ -7436,7 +7425,7 @@
         <v>18</v>
       </c>
       <c r="G118" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H118">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7449,30 +7438,30 @@
         <v>1131</v>
       </c>
       <c r="K118" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L118">
         <v>1</v>
       </c>
       <c r="M118" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P118" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q118" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y118" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>111</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C119" t="s">
         <v>26</v>
@@ -7488,7 +7477,7 @@
         <v>18</v>
       </c>
       <c r="G119" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H119">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7501,30 +7490,30 @@
         <v>785</v>
       </c>
       <c r="K119" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L119">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P119" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q119" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y119" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
         <v>82</v>
@@ -7540,7 +7529,7 @@
         <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H120">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7553,21 +7542,21 @@
         <v>830</v>
       </c>
       <c r="K120" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="Y120" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
         <v>83</v>
@@ -7583,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H121">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7596,21 +7585,21 @@
         <v>719</v>
       </c>
       <c r="K121" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="Y121" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C122" t="s">
         <v>84</v>
@@ -7626,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H122">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7639,21 +7628,21 @@
         <v>830</v>
       </c>
       <c r="K122" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="Y122" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>120</v>
       </c>
       <c r="B123" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C123" t="s">
         <v>73</v>
@@ -7669,7 +7658,7 @@
         <v>3</v>
       </c>
       <c r="G123" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H123">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7682,13 +7671,13 @@
         <v>28</v>
       </c>
       <c r="K123" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="Y123" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -7696,7 +7685,7 @@
         <v>85</v>
       </c>
       <c r="B124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C124" t="s">
         <v>43</v>
@@ -7712,7 +7701,7 @@
         <v>36</v>
       </c>
       <c r="G124" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H124">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7725,22 +7714,22 @@
         <v>726.16783091409297</v>
       </c>
       <c r="K124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L124">
         <v>1</v>
       </c>
       <c r="M124" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P124" t="s">
         <v>124</v>
       </c>
       <c r="Q124" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R124" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y124">
         <v>1</v>
@@ -7751,7 +7740,7 @@
         <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
@@ -7767,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="G125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H125">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7780,22 +7769,22 @@
         <v>723.54111845857994</v>
       </c>
       <c r="K125" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L125">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P125" t="s">
         <v>125</v>
       </c>
       <c r="Q125" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R125" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y125">
         <v>1</v>
@@ -7806,7 +7795,7 @@
         <v>35</v>
       </c>
       <c r="B126" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
@@ -7822,7 +7811,7 @@
         <v>1</v>
       </c>
       <c r="G126" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H126">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7835,42 +7824,42 @@
         <v>723.54111845857994</v>
       </c>
       <c r="K126" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L126">
         <v>1</v>
       </c>
       <c r="M126" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P126" t="s">
         <v>125</v>
       </c>
       <c r="Q126" t="s">
+        <v>200</v>
+      </c>
+      <c r="R126" t="s">
+        <v>211</v>
+      </c>
+      <c r="S126" t="s">
+        <v>204</v>
+      </c>
+      <c r="T126" t="s">
+        <v>203</v>
+      </c>
+      <c r="U126" t="s">
         <v>201</v>
       </c>
-      <c r="R126" t="s">
-        <v>212</v>
-      </c>
-      <c r="S126" t="s">
-        <v>205</v>
-      </c>
-      <c r="T126" t="s">
-        <v>204</v>
-      </c>
-      <c r="U126" t="s">
-        <v>202</v>
-      </c>
       <c r="Y126">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C127" t="s">
         <v>17</v>
@@ -7886,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H127">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7899,28 +7888,28 @@
         <v>50</v>
       </c>
       <c r="K127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L127">
         <v>1</v>
       </c>
       <c r="M127" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P127" t="s">
         <v>125</v>
       </c>
       <c r="Q127" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S127" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T127" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -7928,7 +7917,7 @@
         <v>113</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C128" t="s">
         <v>43</v>
@@ -7944,7 +7933,7 @@
         <v>36</v>
       </c>
       <c r="G128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H128">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -7957,22 +7946,22 @@
         <v>673.531736446026</v>
       </c>
       <c r="K128" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L128">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P128" t="s">
         <v>124</v>
       </c>
       <c r="Q128" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R128" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y128">
         <v>1</v>
@@ -7983,7 +7972,7 @@
         <v>36</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -7999,7 +7988,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H129">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8012,31 +8001,31 @@
         <v>699.61775277647098</v>
       </c>
       <c r="K129" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L129">
         <v>1</v>
       </c>
       <c r="M129" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P129" t="s">
         <v>125</v>
       </c>
       <c r="Q129" t="s">
+        <v>200</v>
+      </c>
+      <c r="R129" t="s">
+        <v>211</v>
+      </c>
+      <c r="S129" t="s">
+        <v>204</v>
+      </c>
+      <c r="T129" t="s">
+        <v>203</v>
+      </c>
+      <c r="U129" t="s">
         <v>201</v>
-      </c>
-      <c r="R129" t="s">
-        <v>212</v>
-      </c>
-      <c r="S129" t="s">
-        <v>205</v>
-      </c>
-      <c r="T129" t="s">
-        <v>204</v>
-      </c>
-      <c r="U129" t="s">
-        <v>202</v>
       </c>
       <c r="Y129">
         <v>1</v>
@@ -8047,7 +8036,7 @@
         <v>107</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C130" t="s">
         <v>37</v>
@@ -8063,7 +8052,7 @@
         <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H130">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8076,19 +8065,19 @@
         <v>919.47049979866097</v>
       </c>
       <c r="K130" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L130">
         <v>1</v>
       </c>
       <c r="M130" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P130" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q130" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y130">
         <v>1</v>
@@ -8099,7 +8088,7 @@
         <v>100</v>
       </c>
       <c r="B131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C131" t="s">
         <v>37</v>
@@ -8115,7 +8104,7 @@
         <v>21</v>
       </c>
       <c r="G131" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H131">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8128,19 +8117,19 @@
         <v>910.35487585885903</v>
       </c>
       <c r="K131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L131">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P131" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q131" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y131">
         <v>1</v>
@@ -8151,7 +8140,7 @@
         <v>66</v>
       </c>
       <c r="B132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C132" t="s">
         <v>65</v>
@@ -8167,7 +8156,7 @@
         <v>5058</v>
       </c>
       <c r="G132" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H132">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8180,54 +8169,54 @@
         <v>1024.49060513017</v>
       </c>
       <c r="K132" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L132">
         <v>1</v>
       </c>
       <c r="M132" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N132" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O132" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P132" t="s">
         <v>130</v>
       </c>
       <c r="Q132" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R132" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S132" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T132" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V132" t="s">
+        <v>226</v>
+      </c>
+      <c r="W132" t="s">
+        <v>200</v>
+      </c>
+      <c r="X132" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y132" t="s">
         <v>227</v>
       </c>
-      <c r="W132" t="s">
-        <v>201</v>
-      </c>
-      <c r="X132" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y132" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>66</v>
       </c>
       <c r="B133" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C133" t="s">
         <v>86</v>
@@ -8243,7 +8232,7 @@
         <v>5058</v>
       </c>
       <c r="G133" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H133">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8256,46 +8245,46 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L133">
         <v>1</v>
       </c>
       <c r="M133" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N133" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P133" t="s">
         <v>130</v>
       </c>
       <c r="Q133" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S133" t="s">
+        <v>207</v>
+      </c>
+      <c r="T133" t="s">
         <v>208</v>
       </c>
-      <c r="T133" t="s">
-        <v>209</v>
-      </c>
       <c r="V133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="W133" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X133" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -8303,7 +8292,7 @@
         <v>38</v>
       </c>
       <c r="B134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C134" t="s">
         <v>1</v>
@@ -8319,7 +8308,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H134">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8332,21 +8321,21 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K134" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L134">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
       <c r="P134" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q134" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y134">
         <v>1</v>
@@ -8357,7 +8346,7 @@
         <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
         <v>68</v>
@@ -8373,7 +8362,7 @@
         <v>47</v>
       </c>
       <c r="G135" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H135">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8386,27 +8375,27 @@
         <v>501.28834017958098</v>
       </c>
       <c r="K135" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L135">
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q135" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y135" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>67</v>
       </c>
       <c r="B136" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C136" t="s">
         <v>68</v>
@@ -8422,7 +8411,7 @@
         <v>47</v>
       </c>
       <c r="G136" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H136">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8435,24 +8424,24 @@
         <v>29</v>
       </c>
       <c r="K136" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L136">
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y136" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>67</v>
       </c>
       <c r="B137" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C137" t="s">
         <v>87</v>
@@ -8468,7 +8457,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H137">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8481,22 +8470,22 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L137">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P137" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q137" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y137" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -8504,7 +8493,7 @@
         <v>118</v>
       </c>
       <c r="B138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C138" t="s">
         <v>69</v>
@@ -8520,7 +8509,7 @@
         <v>5056</v>
       </c>
       <c r="G138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H138">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8533,19 +8522,19 @@
         <v>825.36295046482405</v>
       </c>
       <c r="K138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L138">
         <v>1</v>
       </c>
       <c r="M138" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P138" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q138" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y138">
         <v>1</v>
@@ -8556,7 +8545,7 @@
         <v>104</v>
       </c>
       <c r="B139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C139" t="s">
         <v>1</v>
@@ -8572,7 +8561,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H139">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8585,35 +8574,35 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K139" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L139">
         <v>1</v>
       </c>
       <c r="M139" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
       <c r="P139" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q139" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S139" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y139">
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>39</v>
       </c>
       <c r="B140" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C140" t="s">
         <v>87</v>
@@ -8629,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H140">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8642,25 +8631,25 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L140">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q140" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S140" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y140" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -8668,7 +8657,7 @@
         <v>115</v>
       </c>
       <c r="B141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C141" t="s">
         <v>48</v>
@@ -8684,7 +8673,7 @@
         <v>4992</v>
       </c>
       <c r="G141" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H141">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8697,19 +8686,19 @@
         <v>1678.7468031360499</v>
       </c>
       <c r="K141" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L141">
         <v>1</v>
       </c>
       <c r="M141" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P141" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q141" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y141">
         <v>1</v>
@@ -8720,7 +8709,7 @@
         <v>105</v>
       </c>
       <c r="B142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C142" t="s">
         <v>1</v>
@@ -8736,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="G142" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H142">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8749,19 +8738,19 @@
         <v>603.75491716424096</v>
       </c>
       <c r="K142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L142">
         <v>1</v>
       </c>
       <c r="M142" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q142" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y142">
         <v>1</v>
@@ -8772,7 +8761,7 @@
         <v>98</v>
       </c>
       <c r="B143" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C143" t="s">
         <v>18</v>
@@ -8788,7 +8777,7 @@
         <v>297</v>
       </c>
       <c r="G143" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H143">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8801,25 +8790,25 @@
         <v>669.30561031564605</v>
       </c>
       <c r="K143" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L143">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N143" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P143" t="s">
         <v>129</v>
       </c>
       <c r="Q143" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R143" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y143">
         <v>0</v>
@@ -8830,7 +8819,7 @@
         <v>98</v>
       </c>
       <c r="B144" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C144" t="s">
         <v>26</v>
@@ -8846,7 +8835,7 @@
         <v>18</v>
       </c>
       <c r="G144" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H144">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8859,30 +8848,30 @@
         <v>733.70975187740203</v>
       </c>
       <c r="K144" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L144">
         <v>1</v>
       </c>
       <c r="M144" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P144" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q144" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y144">
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>98</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
         <v>88</v>
@@ -8898,7 +8887,7 @@
         <v>21</v>
       </c>
       <c r="G145" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H145">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8911,30 +8900,30 @@
         <v>699</v>
       </c>
       <c r="K145" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L145">
         <v>1</v>
       </c>
       <c r="M145" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q145" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y145" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>98</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C146" t="s">
         <v>89</v>
@@ -8950,7 +8939,7 @@
         <v>59</v>
       </c>
       <c r="G146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H146">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -8963,22 +8952,22 @@
         <v>899</v>
       </c>
       <c r="K146" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L146">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P146" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q146" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y146" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -8986,7 +8975,7 @@
         <v>90</v>
       </c>
       <c r="B147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9002,7 +8991,7 @@
         <v>297</v>
       </c>
       <c r="G147" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H147">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9015,25 +9004,25 @@
         <v>669.30561031564605</v>
       </c>
       <c r="K147" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L147">
         <v>1</v>
       </c>
       <c r="M147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N147" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P147" t="s">
         <v>129</v>
       </c>
       <c r="Q147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R147" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y147">
         <v>0</v>
@@ -9044,7 +9033,7 @@
         <v>90</v>
       </c>
       <c r="B148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C148" t="s">
         <v>26</v>
@@ -9060,7 +9049,7 @@
         <v>18</v>
       </c>
       <c r="G148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H148">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9073,30 +9062,30 @@
         <v>733.70975187740203</v>
       </c>
       <c r="K148" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L148">
         <v>1</v>
       </c>
       <c r="M148" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P148" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q148" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y148">
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>90</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C149" t="s">
         <v>88</v>
@@ -9112,7 +9101,7 @@
         <v>21</v>
       </c>
       <c r="G149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H149">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9125,30 +9114,30 @@
         <v>699</v>
       </c>
       <c r="K149" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L149">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q149" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y149" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>90</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C150" t="s">
         <v>89</v>
@@ -9164,7 +9153,7 @@
         <v>59</v>
       </c>
       <c r="G150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H150">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9177,22 +9166,22 @@
         <v>899</v>
       </c>
       <c r="K150" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L150">
         <v>1</v>
       </c>
       <c r="M150" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P150" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q150" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y150" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -9200,7 +9189,7 @@
         <v>40</v>
       </c>
       <c r="B151" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C151" t="s">
         <v>43</v>
@@ -9216,7 +9205,7 @@
         <v>36</v>
       </c>
       <c r="G151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H151">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9229,33 +9218,33 @@
         <v>1013.01776884712</v>
       </c>
       <c r="K151" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L151">
         <v>1</v>
       </c>
       <c r="M151" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P151" t="s">
         <v>126</v>
       </c>
       <c r="Q151" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R151" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y151">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>40</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C152" t="s">
         <v>2</v>
@@ -9271,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H152">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9284,21 +9273,21 @@
         <v>1013.61333850734</v>
       </c>
       <c r="K152" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L152">
         <v>0</v>
       </c>
       <c r="Y152" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>91</v>
       </c>
       <c r="B153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C153" t="s">
         <v>92</v>
@@ -9314,7 +9303,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H153">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9327,13 +9316,13 @@
         <v>368</v>
       </c>
       <c r="K153" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L153">
         <v>0</v>
       </c>
       <c r="Y153" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -9341,7 +9330,7 @@
         <v>106</v>
       </c>
       <c r="B154" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
@@ -9357,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H154">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9370,22 +9359,22 @@
         <v>506.32005688101998</v>
       </c>
       <c r="K154" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L154">
         <v>1</v>
       </c>
       <c r="M154" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P154" t="s">
         <v>131</v>
       </c>
       <c r="Q154" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R154" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y154">
         <v>1</v>
@@ -9396,7 +9385,7 @@
         <v>122</v>
       </c>
       <c r="B155" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C155" t="s">
         <v>72</v>
@@ -9412,7 +9401,7 @@
         <v>8539</v>
       </c>
       <c r="G155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H155">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9425,19 +9414,19 @@
         <v>2150.4180083783299</v>
       </c>
       <c r="K155" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L155">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P155" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q155" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y155">
         <v>1</v>
@@ -9448,7 +9437,7 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C156" t="s">
         <v>72</v>
@@ -9464,7 +9453,7 @@
         <v>8539</v>
       </c>
       <c r="G156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H156">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9477,19 +9466,19 @@
         <v>2150.4180083783299</v>
       </c>
       <c r="K156" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L156">
         <v>1</v>
       </c>
       <c r="M156" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P156" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q156" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y156">
         <v>1</v>
@@ -9500,7 +9489,7 @@
         <v>71</v>
       </c>
       <c r="B157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C157" t="s">
         <v>72</v>
@@ -9516,7 +9505,7 @@
         <v>8539</v>
       </c>
       <c r="G157" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H157">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9529,19 +9518,19 @@
         <v>2150.4180083783299</v>
       </c>
       <c r="K157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L157">
         <v>1</v>
       </c>
       <c r="M157" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P157" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q157" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y157">
         <v>1</v>
@@ -9552,7 +9541,7 @@
         <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C158" t="s">
         <v>72</v>
@@ -9568,7 +9557,7 @@
         <v>8539</v>
       </c>
       <c r="G158" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H158">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9581,30 +9570,30 @@
         <v>2150.4180083783299</v>
       </c>
       <c r="K158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L158">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P158" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q158" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y158">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>112</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C159" t="s">
         <v>93</v>
@@ -9620,7 +9609,7 @@
         <v>18</v>
       </c>
       <c r="G159" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H159">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9633,22 +9622,22 @@
         <v>2099</v>
       </c>
       <c r="K159" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L159">
         <v>1</v>
       </c>
       <c r="M159" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q159" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y159" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -9656,7 +9645,7 @@
         <v>108</v>
       </c>
       <c r="B160" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C160" t="s">
         <v>37</v>
@@ -9672,7 +9661,7 @@
         <v>21</v>
       </c>
       <c r="G160" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H160">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9685,19 +9674,19 @@
         <v>910.35487585885903</v>
       </c>
       <c r="K160" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L160">
         <v>1</v>
       </c>
       <c r="M160" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q160" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y160">
         <v>1</v>
@@ -9708,7 +9697,7 @@
         <v>109</v>
       </c>
       <c r="B161" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C161" t="s">
         <v>37</v>
@@ -9724,7 +9713,7 @@
         <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H161">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9737,33 +9726,33 @@
         <v>947.48350909131898</v>
       </c>
       <c r="K161" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L161">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N161" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q161" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y161">
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>109</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C162" t="s">
         <v>94</v>
@@ -9779,7 +9768,7 @@
         <v>21</v>
       </c>
       <c r="G162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H162">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9792,34 +9781,34 @@
         <v>548</v>
       </c>
       <c r="K162" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L162">
         <v>1</v>
       </c>
       <c r="M162" t="s">
+        <v>190</v>
+      </c>
+      <c r="N162" t="s">
         <v>191</v>
       </c>
-      <c r="N162" t="s">
+      <c r="P162" t="s">
         <v>192</v>
       </c>
-      <c r="P162" t="s">
-        <v>193</v>
-      </c>
       <c r="Q162" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S162" t="s">
         <v>132</v>
       </c>
       <c r="T162" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="U162" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y162" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -9827,7 +9816,7 @@
         <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C163" t="s">
         <v>18</v>
@@ -9843,7 +9832,7 @@
         <v>297</v>
       </c>
       <c r="G163" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H163">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9856,36 +9845,36 @@
         <v>1638.48682081575</v>
       </c>
       <c r="K163" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L163">
         <v>1</v>
       </c>
       <c r="M163" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N163" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P163" t="s">
         <v>129</v>
       </c>
       <c r="Q163" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R163" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>42</v>
       </c>
       <c r="B164" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C164" t="s">
         <v>31</v>
@@ -9901,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H164">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9914,13 +9903,13 @@
         <v>1640.3041251826401</v>
       </c>
       <c r="K164" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L164">
         <v>0</v>
       </c>
       <c r="Y164" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="165" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -9928,7 +9917,7 @@
         <v>42</v>
       </c>
       <c r="B165" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>27</v>
@@ -9944,7 +9933,7 @@
         <v>18</v>
       </c>
       <c r="G165" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H165">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -9957,30 +9946,30 @@
         <v>1699.20763866736</v>
       </c>
       <c r="K165" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L165">
         <v>1</v>
       </c>
       <c r="M165" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P165" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q165" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y165">
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>42</v>
       </c>
       <c r="B166" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C166" t="s">
         <v>88</v>
@@ -9996,7 +9985,7 @@
         <v>21</v>
       </c>
       <c r="G166" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H166">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10009,30 +9998,30 @@
         <v>591</v>
       </c>
       <c r="K166" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L166">
         <v>1</v>
       </c>
       <c r="M166" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P166" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q166" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y166" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>42</v>
       </c>
       <c r="B167" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C167" t="s">
         <v>89</v>
@@ -10048,7 +10037,7 @@
         <v>59</v>
       </c>
       <c r="G167" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H167">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10061,30 +10050,30 @@
         <v>791</v>
       </c>
       <c r="K167" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L167">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P167" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q167" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y167" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>42</v>
       </c>
       <c r="B168" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C168" t="s">
         <v>18</v>
@@ -10100,7 +10089,7 @@
         <v>297</v>
       </c>
       <c r="G168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H168">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10113,36 +10102,36 @@
         <v>753</v>
       </c>
       <c r="K168" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L168">
         <v>1</v>
       </c>
       <c r="M168" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N168" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P168" t="s">
         <v>129</v>
       </c>
       <c r="Q168" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R168" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y168" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>41</v>
       </c>
       <c r="B169" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C169" t="s">
         <v>31</v>
@@ -10158,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H169">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10171,21 +10160,21 @@
         <v>752</v>
       </c>
       <c r="K169" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L169">
         <v>0</v>
       </c>
       <c r="Y169" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>42</v>
       </c>
       <c r="B170" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C170" t="s">
         <v>26</v>
@@ -10201,7 +10190,7 @@
         <v>18</v>
       </c>
       <c r="G170" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H170">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10214,22 +10203,22 @@
         <v>842</v>
       </c>
       <c r="K170" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L170">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P170" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q170" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y170" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.55000000000000004">
@@ -10237,7 +10226,7 @@
         <v>49</v>
       </c>
       <c r="B171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C171" t="s">
         <v>47</v>
@@ -10253,7 +10242,7 @@
         <v>4992</v>
       </c>
       <c r="G171" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H171">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10266,19 +10255,19 @@
         <v>3182.8229676845099</v>
       </c>
       <c r="K171" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L171">
         <v>1</v>
       </c>
       <c r="M171" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q171" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y171">
         <v>1</v>
@@ -10289,7 +10278,7 @@
         <v>116</v>
       </c>
       <c r="B172" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C172" t="s">
         <v>47</v>
@@ -10305,7 +10294,7 @@
         <v>4992</v>
       </c>
       <c r="G172" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H172">
         <f>ABS(テーブル1[[#This Row],[after_change]]-テーブル1[[#This Row],[before_change]])</f>
@@ -10318,19 +10307,19 @@
         <v>3182.8229676845099</v>
       </c>
       <c r="K172" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L172">
         <v>1</v>
       </c>
       <c r="M172" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P172" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Y172">
         <v>1</v>
